--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ana.peguero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1363648-6ACE-4942-B905-3C58B61FD6DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F71C663-1F60-4E74-BDBE-0C5034414805}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1628,13 +1628,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6CB4A9B1-93EC-4EED-8676-389C741B5BCD}" name="Table2" displayName="Table2" ref="A1:M660" totalsRowShown="0" headerRowDxfId="9" tableBorderDxfId="8">
-  <autoFilter ref="A1:M660" xr:uid="{6CB4A9B1-93EC-4EED-8676-389C741B5BCD}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="MC16"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M660" xr:uid="{6CB4A9B1-93EC-4EED-8676-389C741B5BCD}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{8AC0A2DD-0C1A-4FCA-B819-ADF08F0E1153}" name="Centro"/>
     <tableColumn id="2" xr3:uid="{20E7D352-5C57-4B37-ACD3-35B64EB01EA1}" name="Formato" dataDxfId="7"/>
@@ -1859,7 +1853,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="2" max="2" width="26.453125" customWidth="1"/>
     <col min="3" max="3" width="14.81640625" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
     <col min="5" max="6" width="16" style="1" customWidth="1"/>
@@ -1913,7 +1907,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>11</v>
       </c>
@@ -1941,7 +1935,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1986,7 +1980,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>11</v>
       </c>
@@ -2031,7 +2025,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="13" t="s">
         <v>11</v>
       </c>
@@ -2074,7 +2068,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>11</v>
       </c>
@@ -2117,7 +2111,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
@@ -2162,7 +2156,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>11</v>
       </c>
@@ -2207,7 +2201,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="13" t="s">
         <v>11</v>
       </c>
@@ -2252,7 +2246,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>11</v>
       </c>
@@ -2295,7 +2289,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="13" t="s">
         <v>11</v>
       </c>
@@ -2340,7 +2334,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="22" t="s">
         <v>11</v>
       </c>
@@ -2383,7 +2377,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="26" t="s">
         <v>11</v>
       </c>
@@ -2428,7 +2422,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="22" t="s">
         <v>35</v>
       </c>
@@ -2473,7 +2467,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="26" t="s">
         <v>35</v>
       </c>
@@ -2518,7 +2512,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>36</v>
       </c>
@@ -2564,7 +2558,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" s="26" t="s">
         <v>36</v>
       </c>
@@ -2609,7 +2603,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
         <v>36</v>
       </c>
@@ -2654,7 +2648,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" s="13" t="s">
         <v>36</v>
       </c>
@@ -2699,7 +2693,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" s="22" t="s">
         <v>41</v>
       </c>
@@ -2744,7 +2738,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" s="13" t="s">
         <v>41</v>
       </c>
@@ -2789,7 +2783,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
         <v>41</v>
       </c>
@@ -2834,7 +2828,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" s="26" t="s">
         <v>41</v>
       </c>
@@ -2879,7 +2873,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>41</v>
       </c>
@@ -2924,7 +2918,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" s="13" t="s">
         <v>42</v>
       </c>
@@ -2951,7 +2945,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
         <v>42</v>
       </c>
@@ -2996,7 +2990,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" s="13" t="s">
         <v>42</v>
       </c>
@@ -3041,7 +3035,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" s="22" t="s">
         <v>46</v>
       </c>
@@ -3086,7 +3080,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" s="26" t="s">
         <v>46</v>
       </c>
@@ -3131,7 +3125,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" s="13" t="s">
         <v>46</v>
       </c>
@@ -3176,7 +3170,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" s="13" t="s">
         <v>46</v>
       </c>
@@ -3221,7 +3215,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" s="22" t="s">
         <v>46</v>
       </c>
@@ -3266,7 +3260,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" s="26" t="s">
         <v>49</v>
       </c>
@@ -3312,7 +3306,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" s="22" t="s">
         <v>49</v>
       </c>
@@ -3355,7 +3349,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" s="13" t="s">
         <v>49</v>
       </c>
@@ -3400,7 +3394,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" s="22" t="s">
         <v>49</v>
       </c>
@@ -3445,7 +3439,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" s="13" t="s">
         <v>52</v>
       </c>
@@ -3490,7 +3484,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="38" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" s="22" t="s">
         <v>52</v>
       </c>
@@ -3536,7 +3530,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" s="26" t="s">
         <v>52</v>
       </c>
@@ -3581,7 +3575,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" s="22" t="s">
         <v>52</v>
       </c>
@@ -3626,7 +3620,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" s="26" t="s">
         <v>52</v>
       </c>
@@ -3672,7 +3666,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="22" t="s">
         <v>52</v>
       </c>
@@ -3717,7 +3711,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A43" s="13" t="s">
         <v>57</v>
       </c>
@@ -3762,7 +3756,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A44" s="22" t="s">
         <v>57</v>
       </c>
@@ -3807,7 +3801,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A45" s="26" t="s">
         <v>57</v>
       </c>
@@ -3852,7 +3846,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
         <v>57</v>
       </c>
@@ -3897,7 +3891,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A47" s="13" t="s">
         <v>57</v>
       </c>
@@ -3942,7 +3936,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A48" s="13" t="s">
         <v>57</v>
       </c>
@@ -3987,7 +3981,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A49" s="26" t="s">
         <v>57</v>
       </c>
@@ -4032,7 +4026,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A50" s="13" t="s">
         <v>62</v>
       </c>
@@ -4077,7 +4071,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A51" s="13" t="s">
         <v>62</v>
       </c>
@@ -4121,7 +4115,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
         <v>65</v>
       </c>
@@ -4166,7 +4160,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A53" s="13" t="s">
         <v>65</v>
       </c>
@@ -4211,7 +4205,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A54" s="22" t="s">
         <v>65</v>
       </c>
@@ -4256,7 +4250,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A55" s="13" t="s">
         <v>65</v>
       </c>
@@ -4301,7 +4295,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="56" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="22" t="s">
         <v>70</v>
       </c>
@@ -4346,7 +4340,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A57" s="26" t="s">
         <v>70</v>
       </c>
@@ -4376,7 +4370,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A58" s="22" t="s">
         <v>70</v>
       </c>
@@ -4421,7 +4415,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A59" s="13" t="s">
         <v>70</v>
       </c>
@@ -4466,7 +4460,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A60" s="13" t="s">
         <v>70</v>
       </c>
@@ -4511,7 +4505,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A61" s="26" t="s">
         <v>70</v>
       </c>
@@ -4556,7 +4550,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A62" s="22" t="s">
         <v>73</v>
       </c>
@@ -4601,7 +4595,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A63" s="26" t="s">
         <v>73</v>
       </c>
@@ -4646,7 +4640,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
         <v>73</v>
       </c>
@@ -4691,7 +4685,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A65" s="13" t="s">
         <v>73</v>
       </c>
@@ -4736,7 +4730,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A66" s="13" t="s">
         <v>74</v>
       </c>
@@ -4781,7 +4775,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A67" s="13" t="s">
         <v>74</v>
       </c>
@@ -4810,7 +4804,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A68" s="13" t="s">
         <v>74</v>
       </c>
@@ -4855,7 +4849,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A69" s="13" t="s">
         <v>76</v>
       </c>
@@ -4900,7 +4894,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A70" s="13" t="s">
         <v>76</v>
       </c>
@@ -4945,7 +4939,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A71" s="26" t="s">
         <v>76</v>
       </c>
@@ -4990,7 +4984,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A72" s="22" t="s">
         <v>76</v>
       </c>
@@ -5035,7 +5029,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="73" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A73" s="26" t="s">
         <v>77</v>
       </c>
@@ -5080,7 +5074,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A74" s="22" t="s">
         <v>77</v>
       </c>
@@ -5125,7 +5119,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A75" s="13" t="s">
         <v>77</v>
       </c>
@@ -5170,7 +5164,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A76" s="13" t="s">
         <v>80</v>
       </c>
@@ -5215,7 +5209,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="77" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A77" s="26" t="s">
         <v>80</v>
       </c>
@@ -5260,7 +5254,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A78" s="22" t="s">
         <v>80</v>
       </c>
@@ -5305,7 +5299,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="79" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A79" s="26" t="s">
         <v>80</v>
       </c>
@@ -5350,7 +5344,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A80" s="22" t="s">
         <v>81</v>
       </c>
@@ -5395,7 +5389,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A81" s="26" t="s">
         <v>81</v>
       </c>
@@ -5424,7 +5418,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
         <v>81</v>
       </c>
@@ -5469,7 +5463,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A83" s="13" t="s">
         <v>81</v>
       </c>
@@ -5514,7 +5508,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A84" s="22" t="s">
         <v>81</v>
       </c>
@@ -5559,7 +5553,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A85" s="13" t="s">
         <v>81</v>
       </c>
@@ -5604,7 +5598,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A86" s="22" t="s">
         <v>82</v>
       </c>
@@ -5649,7 +5643,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A87" s="26" t="s">
         <v>82</v>
       </c>
@@ -5692,7 +5686,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A88" s="13" t="s">
         <v>82</v>
       </c>
@@ -5737,7 +5731,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A89" s="26" t="s">
         <v>82</v>
       </c>
@@ -5782,7 +5776,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A90" s="13" t="s">
         <v>82</v>
       </c>
@@ -5827,7 +5821,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A91" s="26" t="s">
         <v>82</v>
       </c>
@@ -5872,7 +5866,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A92" s="22" t="s">
         <v>82</v>
       </c>
@@ -5899,7 +5893,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A93" s="26" t="s">
         <v>86</v>
       </c>
@@ -5944,7 +5938,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A94" s="22" t="s">
         <v>86</v>
       </c>
@@ -5989,7 +5983,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A95" s="13" t="s">
         <v>86</v>
       </c>
@@ -6034,7 +6028,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A96" s="22" t="s">
         <v>87</v>
       </c>
@@ -6079,7 +6073,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" s="13" t="s">
         <v>87</v>
       </c>
@@ -6124,7 +6118,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" s="13" t="s">
         <v>87</v>
       </c>
@@ -6167,7 +6161,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" s="26" t="s">
         <v>87</v>
       </c>
@@ -6212,7 +6206,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" s="13" t="s">
         <v>87</v>
       </c>
@@ -6257,7 +6251,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" s="13" t="s">
         <v>88</v>
       </c>
@@ -6302,7 +6296,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" s="13" t="s">
         <v>88</v>
       </c>
@@ -6345,7 +6339,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" s="26" t="s">
         <v>88</v>
       </c>
@@ -6390,7 +6384,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" s="22" t="s">
         <v>88</v>
       </c>
@@ -6435,7 +6429,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" s="26" t="s">
         <v>89</v>
       </c>
@@ -6480,7 +6474,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A106" s="13" t="s">
         <v>89</v>
       </c>
@@ -6525,7 +6519,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" s="13" t="s">
         <v>89</v>
       </c>
@@ -6570,7 +6564,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" s="13" t="s">
         <v>89</v>
       </c>
@@ -6615,7 +6609,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" s="13" t="s">
         <v>89</v>
       </c>
@@ -6660,7 +6654,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" s="22" t="s">
         <v>89</v>
       </c>
@@ -6705,7 +6699,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" s="26" t="s">
         <v>89</v>
       </c>
@@ -6750,7 +6744,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" s="13" t="s">
         <v>89</v>
       </c>
@@ -6795,7 +6789,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A113" s="13" t="s">
         <v>94</v>
       </c>
@@ -6841,7 +6835,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="114" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A114" s="13" t="s">
         <v>94</v>
       </c>
@@ -6886,7 +6880,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A115" s="26" t="s">
         <v>94</v>
       </c>
@@ -6931,7 +6925,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A116" s="13" t="s">
         <v>94</v>
       </c>
@@ -6976,7 +6970,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A117" s="26" t="s">
         <v>94</v>
       </c>
@@ -7021,7 +7015,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="118" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A118" s="13" t="s">
         <v>94</v>
       </c>
@@ -7066,7 +7060,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A119" s="26" t="s">
         <v>94</v>
       </c>
@@ -7111,7 +7105,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="120" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A120" s="13" t="s">
         <v>94</v>
       </c>
@@ -7156,7 +7150,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A121" s="13" t="s">
         <v>94</v>
       </c>
@@ -7201,7 +7195,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A122" s="13" t="s">
         <v>98</v>
       </c>
@@ -7244,7 +7238,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A123" s="26" t="s">
         <v>98</v>
       </c>
@@ -7289,7 +7283,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A124" s="13" t="s">
         <v>98</v>
       </c>
@@ -7332,7 +7326,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A125" s="26" t="s">
         <v>98</v>
       </c>
@@ -7377,7 +7371,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A126" s="22" t="s">
         <v>98</v>
       </c>
@@ -7422,7 +7416,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A127" s="13" t="s">
         <v>98</v>
       </c>
@@ -7447,7 +7441,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A128" s="22" t="s">
         <v>104</v>
       </c>
@@ -7492,7 +7486,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A129" s="13" t="s">
         <v>104</v>
       </c>
@@ -7537,7 +7531,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A130" s="13" t="s">
         <v>104</v>
       </c>
@@ -7582,7 +7576,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A131" s="13" t="s">
         <v>104</v>
       </c>
@@ -7627,7 +7621,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A132" s="13" t="s">
         <v>104</v>
       </c>
@@ -7672,7 +7666,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A133" s="26" t="s">
         <v>104</v>
       </c>
@@ -7717,7 +7711,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A134" s="22" t="s">
         <v>105</v>
       </c>
@@ -7762,7 +7756,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A135" s="13" t="s">
         <v>106</v>
       </c>
@@ -7807,7 +7801,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A136" s="22" t="s">
         <v>106</v>
       </c>
@@ -7852,7 +7846,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A137" s="13" t="s">
         <v>106</v>
       </c>
@@ -7879,7 +7873,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A138" s="13" t="s">
         <v>106</v>
       </c>
@@ -7924,7 +7918,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A139" s="26" t="s">
         <v>106</v>
       </c>
@@ -7969,7 +7963,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A140" s="13" t="s">
         <v>106</v>
       </c>
@@ -8012,7 +8006,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A141" s="13" t="s">
         <v>109</v>
       </c>
@@ -8057,7 +8051,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A142" s="13" t="s">
         <v>109</v>
       </c>
@@ -8102,7 +8096,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A143" s="26" t="s">
         <v>109</v>
       </c>
@@ -8147,7 +8141,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A144" s="22" t="s">
         <v>110</v>
       </c>
@@ -8192,7 +8186,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A145" s="26" t="s">
         <v>110</v>
       </c>
@@ -8237,7 +8231,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A146" s="13" t="s">
         <v>110</v>
       </c>
@@ -8282,7 +8276,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A147" s="13" t="s">
         <v>110</v>
       </c>
@@ -8327,7 +8321,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A148" s="22" t="s">
         <v>111</v>
       </c>
@@ -8354,7 +8348,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A149" s="26" t="s">
         <v>111</v>
       </c>
@@ -8399,7 +8393,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A150" s="22" t="s">
         <v>111</v>
       </c>
@@ -8444,7 +8438,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A151" s="26" t="s">
         <v>111</v>
       </c>
@@ -8489,7 +8483,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A152" s="22" t="s">
         <v>111</v>
       </c>
@@ -8534,7 +8528,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A153" s="26" t="s">
         <v>112</v>
       </c>
@@ -8579,7 +8573,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A154" s="13" t="s">
         <v>112</v>
       </c>
@@ -8624,7 +8618,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A155" s="13" t="s">
         <v>112</v>
       </c>
@@ -8669,7 +8663,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A156" s="13" t="s">
         <v>112</v>
       </c>
@@ -8714,7 +8708,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A157" s="13" t="s">
         <v>112</v>
       </c>
@@ -8759,7 +8753,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A158" s="13" t="s">
         <v>112</v>
       </c>
@@ -8804,7 +8798,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A159" s="26" t="s">
         <v>113</v>
       </c>
@@ -8849,7 +8843,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A160" s="22" t="s">
         <v>113</v>
       </c>
@@ -8894,7 +8888,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A161" s="26" t="s">
         <v>113</v>
       </c>
@@ -8923,7 +8917,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A162" s="22" t="s">
         <v>113</v>
       </c>
@@ -8968,7 +8962,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A163" s="13" t="s">
         <v>113</v>
       </c>
@@ -9013,7 +9007,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A164" s="22" t="s">
         <v>114</v>
       </c>
@@ -9056,7 +9050,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A165" s="13" t="s">
         <v>114</v>
       </c>
@@ -9099,7 +9093,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A166" s="13" t="s">
         <v>114</v>
       </c>
@@ -9142,7 +9136,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A167" s="26" t="s">
         <v>114</v>
       </c>
@@ -9169,7 +9163,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A168" s="22" t="s">
         <v>114</v>
       </c>
@@ -9210,7 +9204,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A169" s="13" t="s">
         <v>116</v>
       </c>
@@ -9255,7 +9249,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A170" s="22" t="s">
         <v>116</v>
       </c>
@@ -9300,7 +9294,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="171" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A171" s="26" t="s">
         <v>116</v>
       </c>
@@ -9345,7 +9339,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A172" s="22" t="s">
         <v>116</v>
       </c>
@@ -9390,7 +9384,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A173" s="13" t="s">
         <v>117</v>
       </c>
@@ -9435,7 +9429,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A174" s="22" t="s">
         <v>117</v>
       </c>
@@ -9480,7 +9474,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A175" s="13" t="s">
         <v>117</v>
       </c>
@@ -9525,7 +9519,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A176" s="13" t="s">
         <v>118</v>
       </c>
@@ -9570,7 +9564,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A177" s="26" t="s">
         <v>118</v>
       </c>
@@ -9615,7 +9609,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="178" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A178" s="13" t="s">
         <v>119</v>
       </c>
@@ -9660,7 +9654,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A179" s="13" t="s">
         <v>119</v>
       </c>
@@ -9705,7 +9699,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A180" s="22" t="s">
         <v>119</v>
       </c>
@@ -9750,7 +9744,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A181" s="13" t="s">
         <v>119</v>
       </c>
@@ -9795,7 +9789,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A182" s="22" t="s">
         <v>119</v>
       </c>
@@ -9840,7 +9834,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A183" s="13" t="s">
         <v>119</v>
       </c>
@@ -9885,7 +9879,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A184" s="22" t="s">
         <v>120</v>
       </c>
@@ -9930,7 +9924,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A185" s="13" t="s">
         <v>120</v>
       </c>
@@ -9975,7 +9969,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A186" s="22" t="s">
         <v>120</v>
       </c>
@@ -10020,7 +10014,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A187" s="26" t="s">
         <v>120</v>
       </c>
@@ -10065,7 +10059,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A188" s="13" t="s">
         <v>121</v>
       </c>
@@ -10110,7 +10104,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A189" s="26" t="s">
         <v>121</v>
       </c>
@@ -10155,7 +10149,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A190" s="22" t="s">
         <v>121</v>
       </c>
@@ -10200,7 +10194,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A191" s="26" t="s">
         <v>122</v>
       </c>
@@ -10245,7 +10239,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A192" s="22" t="s">
         <v>123</v>
       </c>
@@ -10290,7 +10284,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A193" s="13" t="s">
         <v>123</v>
       </c>
@@ -10335,7 +10329,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A194" s="13" t="s">
         <v>123</v>
       </c>
@@ -10380,7 +10374,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A195" s="13" t="s">
         <v>124</v>
       </c>
@@ -10425,7 +10419,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A196" s="13" t="s">
         <v>125</v>
       </c>
@@ -10470,7 +10464,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A197" s="26" t="s">
         <v>125</v>
       </c>
@@ -10516,7 +10510,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A198" s="13" t="s">
         <v>128</v>
       </c>
@@ -10561,7 +10555,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A199" s="13" t="s">
         <v>128</v>
       </c>
@@ -10606,7 +10600,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="200" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A200" s="22" t="s">
         <v>128</v>
       </c>
@@ -10651,7 +10645,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A201" s="26" t="s">
         <v>128</v>
       </c>
@@ -10696,7 +10690,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A202" s="22" t="s">
         <v>128</v>
       </c>
@@ -10741,7 +10735,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A203" s="13" t="s">
         <v>128</v>
       </c>
@@ -10786,7 +10780,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A204" s="22" t="s">
         <v>128</v>
       </c>
@@ -10831,7 +10825,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A205" s="26" t="s">
         <v>128</v>
       </c>
@@ -10876,7 +10870,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A206" s="13" t="s">
         <v>128</v>
       </c>
@@ -10921,7 +10915,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A207" s="26" t="s">
         <v>128</v>
       </c>
@@ -10966,7 +10960,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A208" s="13" t="s">
         <v>128</v>
       </c>
@@ -11011,7 +11005,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A209" s="13" t="s">
         <v>128</v>
       </c>
@@ -11056,7 +11050,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A210" s="13" t="s">
         <v>144</v>
       </c>
@@ -11101,7 +11095,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A211" s="26" t="s">
         <v>144</v>
       </c>
@@ -11146,7 +11140,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A212" s="22" t="s">
         <v>144</v>
       </c>
@@ -11191,7 +11185,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A213" s="13" t="s">
         <v>144</v>
       </c>
@@ -11236,7 +11230,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A214" s="13" t="s">
         <v>144</v>
       </c>
@@ -11281,7 +11275,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A215" s="13" t="s">
         <v>144</v>
       </c>
@@ -11326,7 +11320,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A216" s="22" t="s">
         <v>147</v>
       </c>
@@ -11371,7 +11365,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="217" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A217" s="26" t="s">
         <v>147</v>
       </c>
@@ -11416,7 +11410,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A218" s="22" t="s">
         <v>147</v>
       </c>
@@ -11461,7 +11455,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A219" s="26" t="s">
         <v>147</v>
       </c>
@@ -11506,7 +11500,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A220" s="22" t="s">
         <v>147</v>
       </c>
@@ -11551,7 +11545,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A221" s="26" t="s">
         <v>147</v>
       </c>
@@ -11596,7 +11590,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A222" s="22" t="s">
         <v>147</v>
       </c>
@@ -11641,7 +11635,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A223" s="26" t="s">
         <v>147</v>
       </c>
@@ -11686,7 +11680,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A224" s="13" t="s">
         <v>147</v>
       </c>
@@ -11731,7 +11725,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="225" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A225" s="13" t="s">
         <v>154</v>
       </c>
@@ -11776,7 +11770,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A226" s="13" t="s">
         <v>154</v>
       </c>
@@ -11821,7 +11815,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A227" s="13" t="s">
         <v>154</v>
       </c>
@@ -11866,7 +11860,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A228" s="13" t="s">
         <v>154</v>
       </c>
@@ -11911,7 +11905,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A229" s="26" t="s">
         <v>154</v>
       </c>
@@ -11956,7 +11950,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A230" s="22" t="s">
         <v>155</v>
       </c>
@@ -12001,7 +11995,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A231" s="26" t="s">
         <v>155</v>
       </c>
@@ -12047,7 +12041,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A232" s="22" t="s">
         <v>155</v>
       </c>
@@ -12092,7 +12086,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A233" s="26" t="s">
         <v>156</v>
       </c>
@@ -12137,7 +12131,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A234" s="22" t="s">
         <v>156</v>
       </c>
@@ -12164,7 +12158,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A235" s="26" t="s">
         <v>156</v>
       </c>
@@ -12207,7 +12201,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A236" s="13" t="s">
         <v>157</v>
       </c>
@@ -12252,7 +12246,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A237" s="13" t="s">
         <v>157</v>
       </c>
@@ -12297,7 +12291,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A238" s="22" t="s">
         <v>157</v>
       </c>
@@ -12342,7 +12336,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A239" s="26" t="s">
         <v>157</v>
       </c>
@@ -12387,7 +12381,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A240" s="22" t="s">
         <v>157</v>
       </c>
@@ -12432,7 +12426,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A241" s="26" t="s">
         <v>157</v>
       </c>
@@ -12477,7 +12471,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A242" s="22" t="s">
         <v>157</v>
       </c>
@@ -12522,7 +12516,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A243" s="13" t="s">
         <v>160</v>
       </c>
@@ -12567,7 +12561,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A244" s="13" t="s">
         <v>160</v>
       </c>
@@ -12612,7 +12606,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A245" s="26" t="s">
         <v>160</v>
       </c>
@@ -12657,7 +12651,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A246" s="22" t="s">
         <v>160</v>
       </c>
@@ -12702,7 +12696,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A247" s="13" t="s">
         <v>160</v>
       </c>
@@ -12747,7 +12741,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A248" s="22" t="s">
         <v>160</v>
       </c>
@@ -12792,7 +12786,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A249" s="26" t="s">
         <v>160</v>
       </c>
@@ -12837,7 +12831,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A250" s="22" t="s">
         <v>160</v>
       </c>
@@ -12882,7 +12876,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A251" s="13" t="s">
         <v>160</v>
       </c>
@@ -12927,7 +12921,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A252" s="22" t="s">
         <v>160</v>
       </c>
@@ -12972,7 +12966,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A253" s="26" t="s">
         <v>160</v>
       </c>
@@ -13017,7 +13011,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="254" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A254" s="13" t="s">
         <v>169</v>
       </c>
@@ -13063,7 +13057,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A255" s="13" t="s">
         <v>169</v>
       </c>
@@ -13108,7 +13102,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A256" s="13" t="s">
         <v>170</v>
       </c>
@@ -13153,7 +13147,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A257" s="35" t="s">
         <v>169</v>
       </c>
@@ -13196,7 +13190,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A258" s="13" t="s">
         <v>169</v>
       </c>
@@ -13241,7 +13235,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A259" s="26" t="s">
         <v>169</v>
       </c>
@@ -13286,7 +13280,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="260" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A260" s="13" t="s">
         <v>170</v>
       </c>
@@ -13331,7 +13325,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A261" s="13" t="s">
         <v>169</v>
       </c>
@@ -13376,7 +13370,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A262" s="22" t="s">
         <v>170</v>
       </c>
@@ -13421,7 +13415,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A263" s="26" t="s">
         <v>169</v>
       </c>
@@ -13465,7 +13459,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A264" s="22" t="s">
         <v>169</v>
       </c>
@@ -13510,7 +13504,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A265" s="13" t="s">
         <v>169</v>
       </c>
@@ -13555,7 +13549,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A266" s="13" t="s">
         <v>169</v>
       </c>
@@ -13600,7 +13594,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="267" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A267" s="26" t="s">
         <v>179</v>
       </c>
@@ -13645,7 +13639,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A268" s="22" t="s">
         <v>179</v>
       </c>
@@ -13690,7 +13684,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A269" s="26" t="s">
         <v>179</v>
       </c>
@@ -13735,7 +13729,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A270" s="13" t="s">
         <v>179</v>
       </c>
@@ -13780,7 +13774,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A271" s="26" t="s">
         <v>179</v>
       </c>
@@ -13825,7 +13819,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A272" s="35" t="s">
         <v>179</v>
       </c>
@@ -13870,7 +13864,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A273" s="26" t="s">
         <v>179</v>
       </c>
@@ -13915,7 +13909,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A274" s="22" t="s">
         <v>179</v>
       </c>
@@ -13960,7 +13954,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A275" s="13" t="s">
         <v>179</v>
       </c>
@@ -14005,7 +13999,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A276" s="13" t="s">
         <v>179</v>
       </c>
@@ -14050,7 +14044,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A277" s="13" t="s">
         <v>179</v>
       </c>
@@ -14095,7 +14089,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A278" s="13" t="s">
         <v>179</v>
       </c>
@@ -14140,7 +14134,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A279" s="13" t="s">
         <v>179</v>
       </c>
@@ -14185,7 +14179,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A280" s="22" t="s">
         <v>179</v>
       </c>
@@ -14230,7 +14224,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A281" s="13" t="s">
         <v>179</v>
       </c>
@@ -14275,7 +14269,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A282" s="13" t="s">
         <v>186</v>
       </c>
@@ -14322,7 +14316,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="283" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A283" s="26" t="s">
         <v>186</v>
       </c>
@@ -14367,7 +14361,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A284" s="13" t="s">
         <v>186</v>
       </c>
@@ -14412,7 +14406,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A285" s="13" t="s">
         <v>186</v>
       </c>
@@ -14457,7 +14451,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A286" s="35" t="s">
         <v>186</v>
       </c>
@@ -14500,7 +14494,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A287" s="26" t="s">
         <v>186</v>
       </c>
@@ -14545,7 +14539,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A288" s="22" t="s">
         <v>186</v>
       </c>
@@ -14590,7 +14584,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A289" s="13" t="s">
         <v>186</v>
       </c>
@@ -14635,7 +14629,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A290" s="13" t="s">
         <v>186</v>
       </c>
@@ -14680,7 +14674,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="291" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A291" s="13" t="s">
         <v>186</v>
       </c>
@@ -14725,7 +14719,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="292" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A292" s="13" t="s">
         <v>186</v>
       </c>
@@ -14770,7 +14764,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A293" s="26" t="s">
         <v>186</v>
       </c>
@@ -14815,7 +14809,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A294" s="13" t="s">
         <v>186</v>
       </c>
@@ -14860,7 +14854,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A295" s="13" t="s">
         <v>186</v>
       </c>
@@ -14887,7 +14881,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A296" s="22" t="s">
         <v>192</v>
       </c>
@@ -14932,7 +14926,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A297" s="13" t="s">
         <v>192</v>
       </c>
@@ -14977,7 +14971,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A298" s="22" t="s">
         <v>192</v>
       </c>
@@ -15022,7 +15016,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A299" s="13" t="s">
         <v>192</v>
       </c>
@@ -15067,7 +15061,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="300" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A300" s="22" t="s">
         <v>192</v>
       </c>
@@ -15112,7 +15106,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A301" s="39" t="s">
         <v>199</v>
       </c>
@@ -15158,7 +15152,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A302" s="39" t="s">
         <v>199</v>
       </c>
@@ -15201,7 +15195,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A303" s="39" t="s">
         <v>199</v>
       </c>
@@ -15246,7 +15240,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="304" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A304" s="39" t="s">
         <v>199</v>
       </c>
@@ -15291,7 +15285,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A305" s="39" t="s">
         <v>199</v>
       </c>
@@ -15336,7 +15330,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A306" s="35" t="s">
         <v>199</v>
       </c>
@@ -15381,7 +15375,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A307" s="39" t="s">
         <v>199</v>
       </c>
@@ -15426,7 +15420,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="308" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A308" s="39" t="s">
         <v>199</v>
       </c>
@@ -15472,7 +15466,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A309" s="35" t="s">
         <v>199</v>
       </c>
@@ -15499,7 +15493,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A310" s="22" t="s">
         <v>202</v>
       </c>
@@ -15542,7 +15536,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A311" s="13" t="s">
         <v>202</v>
       </c>
@@ -15587,7 +15581,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A312" s="22" t="s">
         <v>202</v>
       </c>
@@ -15632,7 +15626,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="313" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A313" s="13" t="s">
         <v>202</v>
       </c>
@@ -15677,7 +15671,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A314" s="13" t="s">
         <v>202</v>
       </c>
@@ -15720,7 +15714,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A315" s="13" t="s">
         <v>202</v>
       </c>
@@ -15765,7 +15759,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A316" s="13" t="s">
         <v>202</v>
       </c>
@@ -15810,7 +15804,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A317" s="13" t="s">
         <v>202</v>
       </c>
@@ -15855,7 +15849,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A318" s="22" t="s">
         <v>202</v>
       </c>
@@ -15885,7 +15879,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="319" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A319" s="26" t="s">
         <v>202</v>
       </c>
@@ -15930,7 +15924,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A320" s="13" t="s">
         <v>202</v>
       </c>
@@ -15975,7 +15969,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A321" s="26" t="s">
         <v>202</v>
       </c>
@@ -16020,7 +16014,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A322" s="13" t="s">
         <v>205</v>
       </c>
@@ -16065,7 +16059,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A323" s="26" t="s">
         <v>205</v>
       </c>
@@ -16110,7 +16104,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A324" s="22" t="s">
         <v>205</v>
       </c>
@@ -16155,7 +16149,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A325" s="26" t="s">
         <v>205</v>
       </c>
@@ -16200,7 +16194,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A326" s="13" t="s">
         <v>205</v>
       </c>
@@ -16245,7 +16239,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="327" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A327" s="35" t="s">
         <v>205</v>
       </c>
@@ -16290,7 +16284,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="328" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A328" s="13" t="s">
         <v>205</v>
       </c>
@@ -16335,7 +16329,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="329" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A329" s="35" t="s">
         <v>205</v>
       </c>
@@ -16380,7 +16374,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="330" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A330" s="22" t="s">
         <v>205</v>
       </c>
@@ -16425,7 +16419,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="331" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A331" s="13" t="s">
         <v>205</v>
       </c>
@@ -16470,7 +16464,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="332" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A332" s="22" t="s">
         <v>205</v>
       </c>
@@ -16515,7 +16509,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="333" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A333" s="13" t="s">
         <v>205</v>
       </c>
@@ -16560,7 +16554,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="334" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A334" s="22" t="s">
         <v>205</v>
       </c>
@@ -16605,7 +16599,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="335" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A335" s="13" t="s">
         <v>205</v>
       </c>
@@ -16648,7 +16642,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="336" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A336" s="22" t="s">
         <v>205</v>
       </c>
@@ -16693,7 +16687,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A337" s="13" t="s">
         <v>205</v>
       </c>
@@ -16723,7 +16717,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A338" s="22" t="s">
         <v>205</v>
       </c>
@@ -16768,7 +16762,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A339" s="13" t="s">
         <v>205</v>
       </c>
@@ -16813,7 +16807,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A340" s="13" t="s">
         <v>205</v>
       </c>
@@ -16858,7 +16852,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="341" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A341" s="13" t="s">
         <v>205</v>
       </c>
@@ -16904,7 +16898,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A342" s="22" t="s">
         <v>210</v>
       </c>
@@ -16949,7 +16943,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A343" s="13" t="s">
         <v>210</v>
       </c>
@@ -16994,7 +16988,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A344" s="13" t="s">
         <v>210</v>
       </c>
@@ -17024,7 +17018,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A345" s="13" t="s">
         <v>210</v>
       </c>
@@ -17069,7 +17063,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="346" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A346" s="13" t="s">
         <v>210</v>
       </c>
@@ -17114,7 +17108,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="347" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A347" s="26" t="s">
         <v>210</v>
       </c>
@@ -17159,7 +17153,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="348" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A348" s="13" t="s">
         <v>210</v>
       </c>
@@ -17204,7 +17198,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A349" s="26" t="s">
         <v>210</v>
       </c>
@@ -17250,7 +17244,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A350" s="22" t="s">
         <v>212</v>
       </c>
@@ -17295,7 +17289,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A351" s="13" t="s">
         <v>212</v>
       </c>
@@ -17340,7 +17334,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A352" s="22" t="s">
         <v>212</v>
       </c>
@@ -17385,7 +17379,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A353" s="35" t="s">
         <v>212</v>
       </c>
@@ -17430,7 +17424,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A354" s="13" t="s">
         <v>212</v>
       </c>
@@ -17475,7 +17469,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A355" s="26" t="s">
         <v>212</v>
       </c>
@@ -17520,7 +17514,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A356" s="22" t="s">
         <v>212</v>
       </c>
@@ -17565,7 +17559,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="357" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A357" s="26" t="s">
         <v>212</v>
       </c>
@@ -17610,7 +17604,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="358" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A358" s="13" t="s">
         <v>212</v>
       </c>
@@ -17655,7 +17649,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A359" s="13" t="s">
         <v>212</v>
       </c>
@@ -17700,7 +17694,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="360" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A360" s="22" t="s">
         <v>212</v>
       </c>
@@ -17745,7 +17739,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="361" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A361" s="13" t="s">
         <v>215</v>
       </c>
@@ -17790,7 +17784,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="362" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A362" s="22" t="s">
         <v>215</v>
       </c>
@@ -17835,7 +17829,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A363" s="26" t="s">
         <v>215</v>
       </c>
@@ -17880,7 +17874,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A364" s="22" t="s">
         <v>215</v>
       </c>
@@ -17925,7 +17919,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A365" s="35" t="s">
         <v>215</v>
       </c>
@@ -17970,7 +17964,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A366" s="13" t="s">
         <v>215</v>
       </c>
@@ -18015,7 +18009,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A367" s="26" t="s">
         <v>215</v>
       </c>
@@ -18060,7 +18054,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A368" s="35" t="s">
         <v>215</v>
       </c>
@@ -18105,7 +18099,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="369" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A369" s="26" t="s">
         <v>215</v>
       </c>
@@ -18150,7 +18144,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="370" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A370" s="13" t="s">
         <v>215</v>
       </c>
@@ -18195,7 +18189,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="371" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A371" s="26" t="s">
         <v>215</v>
       </c>
@@ -18240,7 +18234,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="372" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A372" s="13" t="s">
         <v>215</v>
       </c>
@@ -18285,7 +18279,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="373" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A373" s="13" t="s">
         <v>224</v>
       </c>
@@ -18331,7 +18325,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="374" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A374" s="13" t="s">
         <v>224</v>
       </c>
@@ -18376,7 +18370,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="375" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A375" s="13" t="s">
         <v>224</v>
       </c>
@@ -18421,7 +18415,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="376" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A376" s="22" t="s">
         <v>224</v>
       </c>
@@ -18466,7 +18460,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A377" s="35" t="s">
         <v>224</v>
       </c>
@@ -18511,7 +18505,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="378" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A378" s="35" t="s">
         <v>224</v>
       </c>
@@ -18556,7 +18550,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="379" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A379" s="26" t="s">
         <v>224</v>
       </c>
@@ -18601,7 +18595,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="380" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A380" s="22" t="s">
         <v>224</v>
       </c>
@@ -18646,7 +18640,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A381" s="13" t="s">
         <v>224</v>
       </c>
@@ -18691,7 +18685,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A382" s="22" t="s">
         <v>224</v>
       </c>
@@ -18736,7 +18730,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A383" s="26" t="s">
         <v>227</v>
       </c>
@@ -18768,7 +18762,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A384" s="13" t="s">
         <v>227</v>
       </c>
@@ -18813,7 +18807,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A385" s="13" t="s">
         <v>227</v>
       </c>
@@ -18858,7 +18852,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="386" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A386" s="22" t="s">
         <v>227</v>
       </c>
@@ -18903,7 +18897,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="387" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A387" s="26" t="s">
         <v>227</v>
       </c>
@@ -18946,7 +18940,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="388" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A388" s="22" t="s">
         <v>227</v>
       </c>
@@ -18991,7 +18985,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A389" s="26" t="s">
         <v>227</v>
       </c>
@@ -19037,7 +19031,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="390" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A390" s="13" t="s">
         <v>227</v>
       </c>
@@ -19082,7 +19076,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A391" s="35" t="s">
         <v>227</v>
       </c>
@@ -19127,7 +19121,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A392" s="13" t="s">
         <v>227</v>
       </c>
@@ -19172,7 +19166,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A393" s="13" t="s">
         <v>227</v>
       </c>
@@ -19217,7 +19211,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="394" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A394" s="22" t="s">
         <v>227</v>
       </c>
@@ -19262,7 +19256,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="395" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A395" s="26" t="s">
         <v>227</v>
       </c>
@@ -19307,7 +19301,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="396" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A396" s="22" t="s">
         <v>230</v>
       </c>
@@ -19352,7 +19346,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A397" s="26" t="s">
         <v>230</v>
       </c>
@@ -19397,7 +19391,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A398" s="22" t="s">
         <v>230</v>
       </c>
@@ -19442,7 +19436,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A399" s="26" t="s">
         <v>230</v>
       </c>
@@ -19487,7 +19481,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A400" s="13" t="s">
         <v>230</v>
       </c>
@@ -19532,7 +19526,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A401" s="26" t="s">
         <v>230</v>
       </c>
@@ -19577,7 +19571,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A402" s="35" t="s">
         <v>230</v>
       </c>
@@ -19620,7 +19614,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="403" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A403" s="26" t="s">
         <v>231</v>
       </c>
@@ -19666,7 +19660,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="404" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A404" s="13" t="s">
         <v>231</v>
       </c>
@@ -19711,7 +19705,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A405" s="26" t="s">
         <v>231</v>
       </c>
@@ -19756,7 +19750,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="406" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A406" s="22" t="s">
         <v>231</v>
       </c>
@@ -19801,7 +19795,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A407" s="13" t="s">
         <v>231</v>
       </c>
@@ -19846,7 +19840,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="408" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A408" s="13" t="s">
         <v>231</v>
       </c>
@@ -19891,7 +19885,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="409" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A409" s="35" t="s">
         <v>231</v>
       </c>
@@ -19934,7 +19928,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="410" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A410" s="13" t="s">
         <v>231</v>
       </c>
@@ -19979,7 +19973,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="411" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A411" s="13" t="s">
         <v>231</v>
       </c>
@@ -20024,7 +20018,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A412" s="13" t="s">
         <v>231</v>
       </c>
@@ -20069,7 +20063,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="413" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A413" s="13" t="s">
         <v>232</v>
       </c>
@@ -20112,7 +20106,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A414" s="13" t="s">
         <v>232</v>
       </c>
@@ -20157,7 +20151,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="415" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A415" s="26" t="s">
         <v>232</v>
       </c>
@@ -20202,7 +20196,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="416" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A416" s="22" t="s">
         <v>233</v>
       </c>
@@ -20247,7 +20241,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="417" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A417" s="35" t="s">
         <v>233</v>
       </c>
@@ -20292,7 +20286,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A418" s="22" t="s">
         <v>233</v>
       </c>
@@ -20337,7 +20331,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A419" s="26" t="s">
         <v>233</v>
       </c>
@@ -20382,7 +20376,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A420" s="22" t="s">
         <v>233</v>
       </c>
@@ -20427,7 +20421,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A421" s="26" t="s">
         <v>233</v>
       </c>
@@ -20472,7 +20466,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="422" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A422" s="13" t="s">
         <v>233</v>
       </c>
@@ -21333,7 +21327,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="443" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A443" s="13" t="s">
         <v>242</v>
       </c>
@@ -21378,7 +21372,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="444" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A444" s="22" t="s">
         <v>242</v>
       </c>
@@ -21423,7 +21417,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="445" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A445" s="13" t="s">
         <v>242</v>
       </c>
@@ -21468,7 +21462,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="446" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A446" s="13" t="s">
         <v>242</v>
       </c>
@@ -21513,7 +21507,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="447" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A447" s="13" t="s">
         <v>242</v>
       </c>
@@ -21558,7 +21552,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="448" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A448" s="13" t="s">
         <v>242</v>
       </c>
@@ -21603,7 +21597,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="449" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A449" s="26" t="s">
         <v>242</v>
       </c>
@@ -21648,7 +21642,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="450" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A450" s="13" t="s">
         <v>242</v>
       </c>
@@ -21693,7 +21687,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="451" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A451" s="35" t="s">
         <v>245</v>
       </c>
@@ -21738,7 +21732,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="452" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A452" s="13" t="s">
         <v>245</v>
       </c>
@@ -21783,7 +21777,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="453" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A453" s="26" t="s">
         <v>245</v>
       </c>
@@ -21828,7 +21822,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="454" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A454" s="35" t="s">
         <v>245</v>
       </c>
@@ -21873,7 +21867,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="455" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A455" s="13" t="s">
         <v>245</v>
       </c>
@@ -21918,7 +21912,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="456" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A456" s="13" t="s">
         <v>245</v>
       </c>
@@ -21948,7 +21942,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="457" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A457" s="26" t="s">
         <v>247</v>
       </c>
@@ -21993,7 +21987,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="458" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A458" s="22" t="s">
         <v>247</v>
       </c>
@@ -22038,7 +22032,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="459" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A459" s="13" t="s">
         <v>247</v>
       </c>
@@ -22083,7 +22077,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="460" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A460" s="22" t="s">
         <v>247</v>
       </c>
@@ -22128,7 +22122,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="461" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A461" s="26" t="s">
         <v>247</v>
       </c>
@@ -22173,7 +22167,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="462" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A462" s="13" t="s">
         <v>247</v>
       </c>
@@ -22218,7 +22212,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="463" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A463" s="13" t="s">
         <v>247</v>
       </c>
@@ -22263,7 +22257,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="464" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A464" s="13" t="s">
         <v>248</v>
       </c>
@@ -22308,7 +22302,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="465" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A465" s="26" t="s">
         <v>248</v>
       </c>
@@ -22353,7 +22347,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="466" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A466" s="22" t="s">
         <v>248</v>
       </c>
@@ -22398,7 +22392,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="467" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A467" s="26" t="s">
         <v>248</v>
       </c>
@@ -22443,7 +22437,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="468" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A468" s="13" t="s">
         <v>248</v>
       </c>
@@ -22488,7 +22482,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="469" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A469" s="13" t="s">
         <v>248</v>
       </c>
@@ -22533,7 +22527,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="470" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A470" s="13" t="s">
         <v>248</v>
       </c>
@@ -22578,7 +22572,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="471" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A471" s="26" t="s">
         <v>248</v>
       </c>
@@ -22623,7 +22617,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="472" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A472" s="35" t="s">
         <v>248</v>
       </c>
@@ -22668,7 +22662,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="473" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A473" s="13" t="s">
         <v>248</v>
       </c>
@@ -22713,7 +22707,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="474" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A474" s="13" t="s">
         <v>248</v>
       </c>
@@ -22758,7 +22752,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="475" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A475" s="26" t="s">
         <v>248</v>
       </c>
@@ -22803,7 +22797,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="476" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A476" s="39" t="s">
         <v>249</v>
       </c>
@@ -22848,7 +22842,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="477" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A477" s="39" t="s">
         <v>249</v>
       </c>
@@ -22893,7 +22887,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="478" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A478" s="39" t="s">
         <v>249</v>
       </c>
@@ -22938,7 +22932,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="479" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A479" s="39" t="s">
         <v>249</v>
       </c>
@@ -22983,7 +22977,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="480" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A480" s="39" t="s">
         <v>249</v>
       </c>
@@ -23028,7 +23022,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="481" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A481" s="39" t="s">
         <v>249</v>
       </c>
@@ -23059,7 +23053,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="482" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A482" s="39" t="s">
         <v>249</v>
       </c>
@@ -23104,7 +23098,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="483" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A483" s="39" t="s">
         <v>249</v>
       </c>
@@ -23149,7 +23143,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="484" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A484" s="39" t="s">
         <v>249</v>
       </c>
@@ -23194,7 +23188,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="485" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A485" s="39" t="s">
         <v>249</v>
       </c>
@@ -23239,7 +23233,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="486" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A486" s="39" t="s">
         <v>249</v>
       </c>
@@ -23284,7 +23278,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="487" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A487" s="39" t="s">
         <v>249</v>
       </c>
@@ -23329,7 +23323,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="488" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A488" s="39" t="s">
         <v>249</v>
       </c>
@@ -23370,7 +23364,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="489" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A489" s="39" t="s">
         <v>249</v>
       </c>
@@ -23415,7 +23409,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="490" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A490" s="39" t="s">
         <v>249</v>
       </c>
@@ -23460,7 +23454,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="491" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A491" s="39" t="s">
         <v>249</v>
       </c>
@@ -23490,7 +23484,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="492" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A492" s="39" t="s">
         <v>249</v>
       </c>
@@ -23520,7 +23514,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="493" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A493" s="39" t="s">
         <v>249</v>
       </c>
@@ -23565,7 +23559,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="494" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A494" s="39" t="s">
         <v>249</v>
       </c>
@@ -23595,7 +23589,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="495" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A495" s="39" t="s">
         <v>256</v>
       </c>
@@ -23640,7 +23634,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="496" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A496" s="39" t="s">
         <v>256</v>
       </c>
@@ -23685,7 +23679,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="497" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A497" s="39" t="s">
         <v>256</v>
       </c>
@@ -23716,7 +23710,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="498" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A498" s="39" t="s">
         <v>256</v>
       </c>
@@ -23761,7 +23755,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="499" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A499" s="39" t="s">
         <v>256</v>
       </c>
@@ -23788,7 +23782,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="500" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A500" s="39" t="s">
         <v>256</v>
       </c>
@@ -23833,7 +23827,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="501" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A501" s="39" t="s">
         <v>256</v>
       </c>
@@ -23878,7 +23872,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="502" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A502" s="39" t="s">
         <v>256</v>
       </c>
@@ -23923,7 +23917,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="503" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A503" s="39" t="s">
         <v>256</v>
       </c>
@@ -23969,7 +23963,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="504" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A504" s="39" t="s">
         <v>256</v>
       </c>
@@ -24014,7 +24008,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="505" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A505" s="39" t="s">
         <v>256</v>
       </c>
@@ -24059,7 +24053,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="506" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A506" s="39" t="s">
         <v>256</v>
       </c>
@@ -24100,7 +24094,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="507" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A507" s="35" t="s">
         <v>261</v>
       </c>
@@ -24145,7 +24139,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="508" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A508" s="22" t="s">
         <v>261</v>
       </c>
@@ -24190,7 +24184,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="509" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A509" s="26" t="s">
         <v>261</v>
       </c>
@@ -24235,7 +24229,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="510" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A510" s="13" t="s">
         <v>261</v>
       </c>
@@ -24280,7 +24274,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="511" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A511" s="26" t="s">
         <v>261</v>
       </c>
@@ -24325,7 +24319,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="512" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A512" s="13" t="s">
         <v>261</v>
       </c>
@@ -24370,7 +24364,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="513" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A513" s="26" t="s">
         <v>261</v>
       </c>
@@ -24415,7 +24409,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="514" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A514" s="13" t="s">
         <v>261</v>
       </c>
@@ -24460,7 +24454,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="515" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A515" s="26" t="s">
         <v>264</v>
       </c>
@@ -24506,7 +24500,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="516" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A516" s="22" t="s">
         <v>264</v>
       </c>
@@ -24551,7 +24545,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="517" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A517" s="26" t="s">
         <v>264</v>
       </c>
@@ -24596,7 +24590,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="518" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A518" s="13" t="s">
         <v>264</v>
       </c>
@@ -24641,7 +24635,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="519" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A519" s="13" t="s">
         <v>264</v>
       </c>
@@ -24682,7 +24676,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="520" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A520" s="22" t="s">
         <v>265</v>
       </c>
@@ -24727,7 +24721,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="521" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A521" s="26" t="s">
         <v>265</v>
       </c>
@@ -24772,7 +24766,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="522" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A522" s="22" t="s">
         <v>265</v>
       </c>
@@ -24817,7 +24811,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="523" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A523" s="26" t="s">
         <v>265</v>
       </c>
@@ -24862,7 +24856,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="524" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A524" s="22" t="s">
         <v>265</v>
       </c>
@@ -24905,7 +24899,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="525" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A525" s="26" t="s">
         <v>265</v>
       </c>
@@ -24950,7 +24944,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="526" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A526" s="22" t="s">
         <v>265</v>
       </c>
@@ -24995,7 +24989,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="527" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A527" s="26" t="s">
         <v>265</v>
       </c>
@@ -25040,7 +25034,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="528" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A528" s="22" t="s">
         <v>265</v>
       </c>
@@ -25085,7 +25079,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="529" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A529" s="26" t="s">
         <v>265</v>
       </c>
@@ -25130,7 +25124,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="530" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A530" s="22" t="s">
         <v>265</v>
       </c>
@@ -25175,7 +25169,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="531" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A531" s="26" t="s">
         <v>265</v>
       </c>
@@ -25220,7 +25214,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="532" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A532" s="22" t="s">
         <v>265</v>
       </c>
@@ -25265,7 +25259,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="533" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A533" s="26" t="s">
         <v>268</v>
       </c>
@@ -25310,7 +25304,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="534" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A534" s="13" t="s">
         <v>268</v>
       </c>
@@ -25355,7 +25349,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="535" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A535" s="26" t="s">
         <v>268</v>
       </c>
@@ -25401,7 +25395,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="536" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A536" s="22" t="s">
         <v>268</v>
       </c>
@@ -25446,7 +25440,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="537" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A537" s="13" t="s">
         <v>268</v>
       </c>
@@ -25489,7 +25483,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="538" spans="1:23" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A538" s="22" t="s">
         <v>269</v>
       </c>
@@ -25544,7 +25538,7 @@
       <c r="V538" s="3"/>
       <c r="W538" s="3"/>
     </row>
-    <row r="539" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A539" s="13" t="s">
         <v>270</v>
       </c>
@@ -25588,7 +25582,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="540" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A540" s="13" t="s">
         <v>270</v>
       </c>
@@ -25633,7 +25627,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="541" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A541" s="13" t="s">
         <v>271</v>
       </c>
@@ -25678,7 +25672,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="542" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A542" s="13" t="s">
         <v>271</v>
       </c>
@@ -25723,7 +25717,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="543" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A543" s="26" t="s">
         <v>271</v>
       </c>
@@ -25768,7 +25762,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="544" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A544" s="22" t="s">
         <v>273</v>
       </c>
@@ -25813,7 +25807,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="545" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A545" s="26" t="s">
         <v>273</v>
       </c>
@@ -25858,7 +25852,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="546" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A546" s="22" t="s">
         <v>273</v>
       </c>
@@ -25903,7 +25897,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="547" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A547" s="26" t="s">
         <v>273</v>
       </c>
@@ -25948,7 +25942,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="548" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A548" s="13" t="s">
         <v>273</v>
       </c>
@@ -25965,22 +25959,23 @@
         <v>92681500</v>
       </c>
       <c r="F548" s="15">
-        <v>10664351.040000001</v>
+        <f>10664351.04</f>
+        <v>10664351.039999999</v>
       </c>
       <c r="G548" s="15">
-        <v>0</v>
+        <v>4245902.59</v>
       </c>
       <c r="H548" s="15">
         <f t="shared" si="102"/>
-        <v>10664351.040000001</v>
+        <v>14910253.629999999</v>
       </c>
       <c r="I548" s="19">
         <f t="shared" si="99"/>
-        <v>82017148.959999993</v>
+        <v>77771246.370000005</v>
       </c>
       <c r="J548" s="20">
         <f t="shared" si="100"/>
-        <v>0.11506450629305742</v>
+        <v>0.16087626581356582</v>
       </c>
       <c r="K548" s="21" t="str">
         <f t="shared" si="101"/>
@@ -25993,7 +25988,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="549" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A549" s="13" t="s">
         <v>273</v>
       </c>
@@ -26036,7 +26031,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="550" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A550" s="13" t="s">
         <v>273</v>
       </c>
@@ -26081,7 +26076,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="551" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A551" s="13" t="s">
         <v>273</v>
       </c>
@@ -26126,7 +26121,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="552" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A552" s="22" t="s">
         <v>273</v>
       </c>
@@ -26171,7 +26166,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="553" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A553" s="13" t="s">
         <v>273</v>
       </c>
@@ -26216,7 +26211,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="554" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A554" s="13" t="s">
         <v>273</v>
       </c>
@@ -26261,7 +26256,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="555" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A555" s="26" t="s">
         <v>273</v>
       </c>
@@ -26306,7 +26301,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="556" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A556" s="13" t="s">
         <v>273</v>
       </c>
@@ -26351,7 +26346,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="557" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A557" s="13" t="s">
         <v>273</v>
       </c>
@@ -26396,7 +26391,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="558" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A558" s="13" t="s">
         <v>273</v>
       </c>
@@ -26441,7 +26436,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="559" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A559" s="26" t="s">
         <v>275</v>
       </c>
@@ -26486,7 +26481,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="560" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A560" s="13" t="s">
         <v>275</v>
       </c>
@@ -26531,7 +26526,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="561" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A561" s="13" t="s">
         <v>275</v>
       </c>
@@ -26576,7 +26571,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="562" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A562" s="13" t="s">
         <v>275</v>
       </c>
@@ -26621,7 +26616,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="563" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A563" s="26" t="s">
         <v>275</v>
       </c>
@@ -26666,7 +26661,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="564" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A564" s="22" t="s">
         <v>280</v>
       </c>
@@ -26711,7 +26706,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="565" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A565" s="13" t="s">
         <v>280</v>
       </c>
@@ -26757,7 +26752,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="566" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A566" s="22" t="s">
         <v>280</v>
       </c>
@@ -26802,7 +26797,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="567" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A567" s="26" t="s">
         <v>280</v>
       </c>
@@ -26847,7 +26842,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="568" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A568" s="22" t="s">
         <v>284</v>
       </c>
@@ -26892,7 +26887,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="569" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A569" s="26" t="s">
         <v>284</v>
       </c>
@@ -26937,7 +26932,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="570" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A570" s="13" t="s">
         <v>284</v>
       </c>
@@ -26982,7 +26977,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="571" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A571" s="13" t="s">
         <v>285</v>
       </c>
@@ -27027,7 +27022,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="572" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A572" s="13" t="s">
         <v>286</v>
       </c>
@@ -27072,7 +27067,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="573" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A573" s="26" t="s">
         <v>286</v>
       </c>
@@ -27117,7 +27112,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="574" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A574" s="13" t="s">
         <v>286</v>
       </c>
@@ -27162,7 +27157,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="575" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A575" s="13" t="s">
         <v>289</v>
       </c>
@@ -27207,7 +27202,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="576" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A576" s="13" t="s">
         <v>289</v>
       </c>
@@ -27252,7 +27247,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="577" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A577" s="26" t="s">
         <v>290</v>
       </c>
@@ -27297,7 +27292,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="578" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A578" s="22" t="s">
         <v>290</v>
       </c>
@@ -27342,7 +27337,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="579" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A579" s="26" t="s">
         <v>290</v>
       </c>
@@ -27387,7 +27382,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="580" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A580" s="13" t="s">
         <v>291</v>
       </c>
@@ -27432,7 +27427,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="581" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A581" s="26" t="s">
         <v>291</v>
       </c>
@@ -27477,7 +27472,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="582" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A582" s="22" t="s">
         <v>291</v>
       </c>
@@ -27522,7 +27517,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="583" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A583" s="26" t="s">
         <v>291</v>
       </c>
@@ -27567,7 +27562,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="584" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A584" s="13" t="s">
         <v>291</v>
       </c>
@@ -27612,7 +27607,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="585" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A585" s="13" t="s">
         <v>292</v>
       </c>
@@ -27657,7 +27652,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="586" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A586" s="22" t="s">
         <v>292</v>
       </c>
@@ -27702,7 +27697,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="587" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A587" s="13" t="s">
         <v>292</v>
       </c>
@@ -27747,7 +27742,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="588" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A588" s="22" t="s">
         <v>292</v>
       </c>
@@ -27792,7 +27787,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="589" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A589" s="26" t="s">
         <v>292</v>
       </c>
@@ -27837,7 +27832,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="590" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A590" s="35" t="s">
         <v>292</v>
       </c>
@@ -27882,7 +27877,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="591" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A591" s="13" t="s">
         <v>292</v>
       </c>
@@ -27927,7 +27922,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="592" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A592" s="13" t="s">
         <v>292</v>
       </c>
@@ -27972,7 +27967,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="593" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A593" s="35" t="s">
         <v>292</v>
       </c>
@@ -28017,7 +28012,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="594" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A594" s="22" t="s">
         <v>295</v>
       </c>
@@ -28062,7 +28057,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="595" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A595" s="26" t="s">
         <v>295</v>
       </c>
@@ -28107,7 +28102,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="596" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A596" s="35" t="s">
         <v>295</v>
       </c>
@@ -28153,7 +28148,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="597" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A597" s="26" t="s">
         <v>295</v>
       </c>
@@ -28198,7 +28193,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="598" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A598" s="35" t="s">
         <v>295</v>
       </c>
@@ -28225,7 +28220,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="599" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A599" s="26" t="s">
         <v>295</v>
       </c>
@@ -28270,7 +28265,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="600" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A600" s="13" t="s">
         <v>295</v>
       </c>
@@ -28315,7 +28310,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="601" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A601" s="26" t="s">
         <v>295</v>
       </c>
@@ -28360,7 +28355,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="602" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A602" s="22" t="s">
         <v>295</v>
       </c>
@@ -28405,7 +28400,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="603" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A603" s="26" t="s">
         <v>297</v>
       </c>
@@ -28433,7 +28428,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="604" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A604" s="22" t="s">
         <v>297</v>
       </c>
@@ -28478,7 +28473,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="605" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A605" s="26" t="s">
         <v>297</v>
       </c>
@@ -28523,7 +28518,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="606" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A606" s="13" t="s">
         <v>297</v>
       </c>
@@ -28551,7 +28546,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="607" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A607" s="26" t="s">
         <v>297</v>
       </c>
@@ -28596,7 +28591,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="608" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A608" s="13" t="s">
         <v>297</v>
       </c>
@@ -28641,7 +28636,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="609" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A609" s="13" t="s">
         <v>297</v>
       </c>
@@ -28686,7 +28681,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="610" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A610" s="22" t="s">
         <v>297</v>
       </c>
@@ -28731,7 +28726,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="611" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A611" s="35" t="s">
         <v>297</v>
       </c>
@@ -28776,7 +28771,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="612" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A612" s="13" t="s">
         <v>297</v>
       </c>
@@ -28821,7 +28816,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="613" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A613" s="26" t="s">
         <v>297</v>
       </c>
@@ -28866,7 +28861,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="614" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A614" s="22" t="s">
         <v>297</v>
       </c>
@@ -28911,7 +28906,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="615" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A615" s="26" t="s">
         <v>297</v>
       </c>
@@ -28956,7 +28951,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="616" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A616" s="13" t="s">
         <v>301</v>
       </c>
@@ -28983,7 +28978,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="617" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A617" s="26" t="s">
         <v>301</v>
       </c>
@@ -29028,7 +29023,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="618" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A618" s="13" t="s">
         <v>301</v>
       </c>
@@ -29073,7 +29068,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="619" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A619" s="26" t="s">
         <v>301</v>
       </c>
@@ -29119,7 +29114,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="620" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A620" s="22" t="s">
         <v>301</v>
       </c>
@@ -29164,7 +29159,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="621" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A621" s="13" t="s">
         <v>303</v>
       </c>
@@ -29209,7 +29204,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="622" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A622" s="35" t="s">
         <v>301</v>
       </c>
@@ -29254,7 +29249,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="623" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A623" s="13" t="s">
         <v>301</v>
       </c>
@@ -29299,7 +29294,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="624" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A624" s="22" t="s">
         <v>301</v>
       </c>
@@ -29344,7 +29339,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="625" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A625" s="26" t="s">
         <v>301</v>
       </c>
@@ -29389,7 +29384,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="626" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A626" s="13" t="s">
         <v>301</v>
       </c>
@@ -29434,7 +29429,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="627" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A627" s="26" t="s">
         <v>301</v>
       </c>
@@ -29479,7 +29474,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="628" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A628" s="13" t="s">
         <v>304</v>
       </c>
@@ -29524,7 +29519,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="629" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A629" s="26" t="s">
         <v>304</v>
       </c>
@@ -29569,7 +29564,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="630" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A630" s="22" t="s">
         <v>304</v>
       </c>
@@ -29614,7 +29609,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="631" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A631" s="26" t="s">
         <v>305</v>
       </c>
@@ -29659,7 +29654,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="632" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A632" s="13" t="s">
         <v>305</v>
       </c>
@@ -29704,7 +29699,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="633" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A633" s="13" t="s">
         <v>305</v>
       </c>
@@ -29749,7 +29744,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="634" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A634" s="13" t="s">
         <v>305</v>
       </c>
@@ -29794,7 +29789,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="635" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A635" s="13" t="s">
         <v>305</v>
       </c>
@@ -29839,7 +29834,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="636" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A636" s="13" t="s">
         <v>305</v>
       </c>
@@ -29884,7 +29879,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="637" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A637" s="26" t="s">
         <v>305</v>
       </c>
@@ -29929,7 +29924,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="638" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A638" s="13" t="s">
         <v>305</v>
       </c>
@@ -29974,7 +29969,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="639" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A639" s="13" t="s">
         <v>305</v>
       </c>
@@ -30019,7 +30014,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="640" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A640" s="22" t="s">
         <v>305</v>
       </c>
@@ -30064,7 +30059,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="641" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A641" s="13" t="s">
         <v>305</v>
       </c>
@@ -30109,7 +30104,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="642" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A642" s="13" t="s">
         <v>305</v>
       </c>
@@ -30154,7 +30149,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="643" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A643" s="13" t="s">
         <v>305</v>
       </c>
@@ -30199,7 +30194,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="644" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A644" s="13" t="s">
         <v>307</v>
       </c>
@@ -30244,7 +30239,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="645" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A645" s="13" t="s">
         <v>307</v>
       </c>
@@ -30289,7 +30284,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="646" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A646" s="13" t="s">
         <v>307</v>
       </c>
@@ -30334,7 +30329,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="647" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A647" s="13" t="s">
         <v>307</v>
       </c>
@@ -30379,7 +30374,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="648" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A648" s="22" t="s">
         <v>307</v>
       </c>
@@ -30424,7 +30419,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="649" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A649" s="13" t="s">
         <v>307</v>
       </c>
@@ -30469,7 +30464,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="650" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A650" s="22" t="s">
         <v>307</v>
       </c>
@@ -30514,7 +30509,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="651" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A651" s="26" t="s">
         <v>307</v>
       </c>
@@ -30559,7 +30554,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="652" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A652" s="22" t="s">
         <v>308</v>
       </c>
@@ -30586,7 +30581,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="653" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A653" s="13" t="s">
         <v>308</v>
       </c>
@@ -30631,7 +30626,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="654" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A654" s="22" t="s">
         <v>308</v>
       </c>
@@ -30676,7 +30671,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="655" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A655" s="13" t="s">
         <v>308</v>
       </c>
@@ -30721,7 +30716,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="656" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A656" s="13" t="s">
         <v>310</v>
       </c>
@@ -30766,7 +30761,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="657" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A657" s="26" t="s">
         <v>311</v>
       </c>
@@ -30812,7 +30807,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="658" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A658" s="22" t="s">
         <v>311</v>
       </c>
@@ -30857,7 +30852,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="659" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A659" s="45" t="s">
         <v>311</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ana.peguero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D03E0F7F-4EE1-40FB-97B8-68E0CAB29E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A112054-9543-4990-A476-711DB5961B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Detalle Centro-Supra" sheetId="4" r:id="rId1"/>
@@ -3899,23 +3899,23 @@
         <v>0</v>
       </c>
       <c r="G38" s="15">
-        <v>0</v>
+        <v>3081528.45</v>
       </c>
       <c r="H38" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3081528.45</v>
       </c>
       <c r="I38" s="60">
         <f t="shared" si="3"/>
-        <v>4780000</v>
+        <v>1698471.5499999998</v>
       </c>
       <c r="J38" s="18">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.64467122384937248</v>
       </c>
       <c r="K38" s="19" t="str">
         <f t="shared" si="7"/>
-        <v>Pendiente de ejecutar</v>
+        <v>En Progreso</v>
       </c>
       <c r="L38" s="6" t="s">
         <v>328</v>
@@ -3944,23 +3944,23 @@
         <v>0</v>
       </c>
       <c r="G39" s="31">
-        <v>0</v>
+        <v>3081528.45</v>
       </c>
       <c r="H39" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>3081528.45</v>
       </c>
       <c r="I39" s="60">
         <f t="shared" si="3"/>
-        <v>4780000</v>
+        <v>1698471.5499999998</v>
       </c>
       <c r="J39" s="18">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>0.64467122384937248</v>
       </c>
       <c r="K39" s="19" t="str">
         <f t="shared" si="7"/>
-        <v>Pendiente de ejecutar</v>
+        <v>En Progreso</v>
       </c>
       <c r="L39" s="6" t="s">
         <v>328</v>
@@ -4843,23 +4843,23 @@
         <v>0</v>
       </c>
       <c r="G59" s="15">
-        <v>0</v>
+        <v>2555413.83</v>
       </c>
       <c r="H59" s="50">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>2555413.83</v>
       </c>
       <c r="I59" s="60">
         <f t="shared" si="3"/>
-        <v>3300000</v>
+        <v>744586.16999999993</v>
       </c>
       <c r="J59" s="25">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>0.77436782727272735</v>
       </c>
       <c r="K59" s="26" t="str">
         <f t="shared" si="9"/>
-        <v>Pendiente de ejecutar</v>
+        <v>En Progreso</v>
       </c>
       <c r="L59" s="6" t="s">
         <v>328</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ana.peguero\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1A112054-9543-4990-A476-711DB5961B1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D89E384-9E2E-4A62-A950-97E23E12ADCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1111,23 +1111,27 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1329,7 +1333,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -1455,6 +1459,9 @@
     <xf numFmtId="43" fontId="5" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Currency" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1464,6 +1471,16 @@
     <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="21">
+    <dxf>
+      <font>
+        <u val="none"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1885,16 +1902,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <u val="none"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1977,27 +1984,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6CB4A9B1-93EC-4EED-8676-389C741B5BCD}" name="Table2" displayName="Table2" ref="A1:M685" totalsRowShown="0" headerRowDxfId="19" tableBorderDxfId="18">
-  <autoFilter ref="A1:M685" xr:uid="{6CB4A9B1-93EC-4EED-8676-389C741B5BCD}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{6CB4A9B1-93EC-4EED-8676-389C741B5BCD}" name="Table2" displayName="Table2" ref="A1:M685" totalsRowShown="0" headerRowDxfId="20" tableBorderDxfId="19">
+  <autoFilter ref="A1:M685" xr:uid="{6CB4A9B1-93EC-4EED-8676-389C741B5BCD}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="Hornos de pan"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A27:M630">
     <sortCondition descending="1" ref="F1:F679"/>
   </sortState>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{8AC0A2DD-0C1A-4FCA-B819-ADF08F0E1153}" name="Centro" totalsRowDxfId="17"/>
-    <tableColumn id="2" xr3:uid="{20E7D352-5C57-4B37-ACD3-35B64EB01EA1}" name="Formato" dataDxfId="16" totalsRowDxfId="15"/>
+    <tableColumn id="1" xr3:uid="{8AC0A2DD-0C1A-4FCA-B819-ADF08F0E1153}" name="Centro" totalsRowDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{20E7D352-5C57-4B37-ACD3-35B64EB01EA1}" name="Formato" dataDxfId="17" totalsRowDxfId="16"/>
     <tableColumn id="3" xr3:uid="{B2F2E5D8-43B5-43A4-9FEB-A28FA2CC54FC}" name="Supranumero"/>
-    <tableColumn id="4" xr3:uid="{94A9E106-20B9-4AC0-888E-3ABF496978B7}" name="Descripcion" totalsRowDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{89DF095A-ACCD-4999-805E-52E1C35EC87D}" name="Plan (RD$)" dataDxfId="13" totalsRowDxfId="12" dataCellStyle="Currency"/>
-    <tableColumn id="6" xr3:uid="{E674E612-59B5-4FB6-9D32-F2347C393AF5}" name="Real (RD$)" dataDxfId="11" totalsRowDxfId="10" dataCellStyle="Currency"/>
-    <tableColumn id="7" xr3:uid="{91333904-24DD-4457-8ECB-970E8151ED53}" name="Comprometido (RD$)" dataDxfId="9" totalsRowDxfId="8" dataCellStyle="Currency"/>
-    <tableColumn id="8" xr3:uid="{C8C6B389-5D6A-4F2D-A800-ADD423E421ED}" name="Ejecutado Total (RD$)" dataDxfId="7" totalsRowDxfId="6" dataCellStyle="Currency"/>
-    <tableColumn id="9" xr3:uid="{94256958-09A6-4DAC-8EA1-539981BD02CA}" name="Pendiente (RD$)" dataDxfId="5" totalsRowDxfId="4">
+    <tableColumn id="4" xr3:uid="{94A9E106-20B9-4AC0-888E-3ABF496978B7}" name="Descripcion" totalsRowDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{89DF095A-ACCD-4999-805E-52E1C35EC87D}" name="Plan (RD$)" dataDxfId="14" totalsRowDxfId="13" dataCellStyle="Currency"/>
+    <tableColumn id="6" xr3:uid="{E674E612-59B5-4FB6-9D32-F2347C393AF5}" name="Real (RD$)" dataDxfId="12" totalsRowDxfId="11" dataCellStyle="Currency"/>
+    <tableColumn id="7" xr3:uid="{91333904-24DD-4457-8ECB-970E8151ED53}" name="Comprometido (RD$)" dataDxfId="10" totalsRowDxfId="9" dataCellStyle="Currency"/>
+    <tableColumn id="8" xr3:uid="{C8C6B389-5D6A-4F2D-A800-ADD423E421ED}" name="Ejecutado Total (RD$)" dataDxfId="8" totalsRowDxfId="7" dataCellStyle="Currency"/>
+    <tableColumn id="9" xr3:uid="{94256958-09A6-4DAC-8EA1-539981BD02CA}" name="Pendiente (RD$)" dataDxfId="6" totalsRowDxfId="5">
       <calculatedColumnFormula>E2-H2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="10" xr3:uid="{3CC536C0-115A-46F1-8ED0-3BC7E81DCB70}" name="% Ejecucion"/>
     <tableColumn id="11" xr3:uid="{A1D2E4D4-C81A-4EDB-BB42-30DEBC7713EA}" name="Estatus"/>
-    <tableColumn id="12" xr3:uid="{FDD485DD-F89D-4475-A5E2-66DB744CB1F7}" name="Responsable" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{30D2EA82-1FA5-4B65-B618-265D9A3BEB45}" name="Tipo de Match" dataDxfId="1" totalsRowDxfId="0"/>
+    <tableColumn id="12" xr3:uid="{FDD485DD-F89D-4475-A5E2-66DB744CB1F7}" name="Responsable" dataDxfId="4" totalsRowDxfId="3"/>
+    <tableColumn id="13" xr3:uid="{30D2EA82-1FA5-4B65-B618-265D9A3BEB45}" name="Tipo de Match" dataDxfId="2" totalsRowDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2012,7 +2025,7 @@
       <calculatedColumnFormula>+B1/2</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Ejecutado"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="% Avance" dataDxfId="20">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0100-000004000000}" name="% Avance" dataDxfId="0">
       <calculatedColumnFormula>+#REF!/B2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2262,7 +2275,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" s="38" t="s">
         <v>270</v>
       </c>
@@ -2308,7 +2321,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" s="61" t="s">
         <v>147</v>
       </c>
@@ -2353,7 +2366,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" s="38" t="s">
         <v>213</v>
       </c>
@@ -2398,7 +2411,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="61" t="s">
         <v>147</v>
       </c>
@@ -2443,7 +2456,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" s="38" t="s">
         <v>243</v>
       </c>
@@ -2488,7 +2501,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" s="63" t="s">
         <v>231</v>
       </c>
@@ -2533,7 +2546,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="38" t="s">
         <v>169</v>
       </c>
@@ -2579,7 +2592,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="61" t="s">
         <v>229</v>
       </c>
@@ -2625,7 +2638,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="70" t="s">
         <v>11</v>
       </c>
@@ -2667,7 +2680,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="61" t="s">
         <v>297</v>
       </c>
@@ -2712,7 +2725,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" s="38" t="s">
         <v>210</v>
       </c>
@@ -2757,7 +2770,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="70" t="s">
         <v>11</v>
       </c>
@@ -2802,7 +2815,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="70" t="s">
         <v>11</v>
       </c>
@@ -2845,7 +2858,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" s="70" t="s">
         <v>65</v>
       </c>
@@ -2890,7 +2903,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" s="11" t="s">
         <v>74</v>
       </c>
@@ -2935,7 +2948,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="20" t="s">
         <v>113</v>
       </c>
@@ -2980,7 +2993,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" s="20" t="s">
         <v>41</v>
       </c>
@@ -3025,7 +3038,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" s="20" t="s">
         <v>70</v>
       </c>
@@ -3070,7 +3083,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>57</v>
       </c>
@@ -3116,7 +3129,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" s="38" t="s">
         <v>186</v>
       </c>
@@ -3161,7 +3174,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" s="61" t="s">
         <v>125</v>
       </c>
@@ -3207,7 +3220,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" s="38" t="s">
         <v>270</v>
       </c>
@@ -3252,7 +3265,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" s="63" t="s">
         <v>270</v>
       </c>
@@ -3297,7 +3310,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" s="38" t="s">
         <v>210</v>
       </c>
@@ -3342,7 +3355,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" s="38" t="s">
         <v>128</v>
       </c>
@@ -3387,7 +3400,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" s="61" t="s">
         <v>246</v>
       </c>
@@ -3430,7 +3443,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" s="38" t="s">
         <v>268</v>
       </c>
@@ -3475,7 +3488,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" s="63" t="s">
         <v>205</v>
       </c>
@@ -3518,7 +3531,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="38" t="s">
         <v>205</v>
       </c>
@@ -3564,7 +3577,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="38" t="s">
         <v>169</v>
       </c>
@@ -3609,7 +3622,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="38" t="s">
         <v>289</v>
       </c>
@@ -3654,7 +3667,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="38" t="s">
         <v>240</v>
       </c>
@@ -3699,7 +3712,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="63" t="s">
         <v>277</v>
       </c>
@@ -3744,7 +3757,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="38" t="s">
         <v>128</v>
       </c>
@@ -3789,7 +3802,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="63" t="s">
         <v>210</v>
       </c>
@@ -3872,8 +3885,8 @@
         <f t="shared" si="7"/>
         <v>Pendiente de ejecutar</v>
       </c>
-      <c r="L37" s="6" t="s">
-        <v>328</v>
+      <c r="L37" s="107" t="s">
+        <v>331</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>327</v>
@@ -3917,8 +3930,8 @@
         <f t="shared" si="7"/>
         <v>En Progreso</v>
       </c>
-      <c r="L38" s="6" t="s">
-        <v>328</v>
+      <c r="L38" s="107" t="s">
+        <v>331</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>327</v>
@@ -3962,14 +3975,14 @@
         <f t="shared" si="7"/>
         <v>En Progreso</v>
       </c>
-      <c r="L39" s="6" t="s">
-        <v>328</v>
+      <c r="L39" s="107" t="s">
+        <v>331</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" s="23" t="s">
         <v>128</v>
       </c>
@@ -4014,7 +4027,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A41" s="11" t="s">
         <v>144</v>
       </c>
@@ -4059,7 +4072,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A42" s="32" t="s">
         <v>222</v>
       </c>
@@ -4104,7 +4117,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A43" s="11" t="s">
         <v>294</v>
       </c>
@@ -4149,7 +4162,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A44" s="61" t="s">
         <v>246</v>
       </c>
@@ -4194,7 +4207,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A45" s="11" t="s">
         <v>160</v>
       </c>
@@ -4239,7 +4252,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A46" s="23" t="s">
         <v>268</v>
       </c>
@@ -4284,7 +4297,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A47" s="11" t="s">
         <v>225</v>
       </c>
@@ -4329,7 +4342,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A48" s="20" t="s">
         <v>288</v>
       </c>
@@ -4374,7 +4387,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A49" s="32" t="s">
         <v>212</v>
       </c>
@@ -4419,7 +4432,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A50" s="23" t="s">
         <v>292</v>
       </c>
@@ -4464,7 +4477,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A51" s="23" t="s">
         <v>144</v>
       </c>
@@ -4509,7 +4522,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A52" s="11" t="s">
         <v>202</v>
       </c>
@@ -4554,7 +4567,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A53" s="11" t="s">
         <v>232</v>
       </c>
@@ -4599,7 +4612,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="54" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A54" s="23" t="s">
         <v>294</v>
       </c>
@@ -4644,7 +4657,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A55" s="11" t="s">
         <v>268</v>
       </c>
@@ -4689,7 +4702,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A56" s="20" t="s">
         <v>82</v>
       </c>
@@ -4733,7 +4746,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A57" s="23" t="s">
         <v>213</v>
       </c>
@@ -4778,7 +4791,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A58" s="11" t="s">
         <v>272</v>
       </c>
@@ -4861,14 +4874,14 @@
         <f t="shared" si="9"/>
         <v>En Progreso</v>
       </c>
-      <c r="L59" s="6" t="s">
-        <v>328</v>
+      <c r="L59" s="107" t="s">
+        <v>331</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A60" s="11" t="s">
         <v>202</v>
       </c>
@@ -4913,7 +4926,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="61" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A61" s="23" t="s">
         <v>262</v>
       </c>
@@ -4958,7 +4971,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A62" s="11" t="s">
         <v>94</v>
       </c>
@@ -5001,7 +5014,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A63" s="23" t="s">
         <v>270</v>
       </c>
@@ -5046,7 +5059,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A64" s="11" t="s">
         <v>154</v>
       </c>
@@ -5091,7 +5104,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="65" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A65" s="23" t="s">
         <v>160</v>
       </c>
@@ -5136,7 +5149,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="66" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A66" s="11" t="s">
         <v>186</v>
       </c>
@@ -5182,7 +5195,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="67" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A67" s="23" t="s">
         <v>232</v>
       </c>
@@ -5227,7 +5240,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="68" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A68" s="11" t="s">
         <v>283</v>
       </c>
@@ -5272,7 +5285,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="69" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A69" s="20" t="s">
         <v>240</v>
       </c>
@@ -5317,7 +5330,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="70" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A70" s="36" t="s">
         <v>253</v>
       </c>
@@ -5362,7 +5375,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A71" s="20" t="s">
         <v>49</v>
       </c>
@@ -5405,7 +5418,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="72" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A72" s="11" t="s">
         <v>229</v>
       </c>
@@ -5488,14 +5501,14 @@
         <f t="shared" si="9"/>
         <v>Pendiente de ejecutar</v>
       </c>
-      <c r="L73" s="6" t="s">
-        <v>328</v>
+      <c r="L73" s="107" t="s">
+        <v>331</v>
       </c>
       <c r="M73" s="6" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="74" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A74" s="11" t="s">
         <v>297</v>
       </c>
@@ -5538,7 +5551,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="75" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A75" s="23" t="s">
         <v>128</v>
       </c>
@@ -5583,7 +5596,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="76" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A76" s="70" t="s">
         <v>11</v>
       </c>
@@ -5628,7 +5641,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="77" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A77" s="63" t="s">
         <v>205</v>
       </c>
@@ -5673,7 +5686,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="78" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A78" s="11" t="s">
         <v>160</v>
       </c>
@@ -5718,7 +5731,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A79" s="63" t="s">
         <v>205</v>
       </c>
@@ -5763,7 +5776,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A80" s="11" t="s">
         <v>232</v>
       </c>
@@ -5808,7 +5821,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A81" s="61" t="s">
         <v>246</v>
       </c>
@@ -5851,7 +5864,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="82" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A82" s="11" t="s">
         <v>289</v>
       </c>
@@ -5896,7 +5909,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="83" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A83" s="20" t="s">
         <v>294</v>
       </c>
@@ -5941,7 +5954,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A84" s="36" t="s">
         <v>253</v>
       </c>
@@ -5986,7 +5999,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A85" s="20" t="s">
         <v>229</v>
       </c>
@@ -6021,7 +6034,7 @@
         <v>0</v>
       </c>
       <c r="K85" s="22" t="str">
-        <f t="shared" ref="K85:K116" si="13">IF(E85=0,"Sin Plan",IF(J85&gt;=1,"Completado",IF(J85&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
+        <f t="shared" ref="K85:K102" si="13">IF(E85=0,"Sin Plan",IF(J85&gt;=1,"Completado",IF(J85&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
         <v>Pendiente de ejecutar</v>
       </c>
       <c r="L85" s="6" t="s">
@@ -6031,7 +6044,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="86" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A86" s="11" t="s">
         <v>300</v>
       </c>
@@ -6076,7 +6089,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A87" s="20" t="s">
         <v>212</v>
       </c>
@@ -6121,7 +6134,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A88" s="11" t="s">
         <v>62</v>
       </c>
@@ -6167,7 +6180,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A89" s="23" t="s">
         <v>222</v>
       </c>
@@ -6212,7 +6225,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" s="71" t="s">
         <v>73</v>
       </c>
@@ -6257,7 +6270,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" s="70" t="s">
         <v>76</v>
       </c>
@@ -6302,7 +6315,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="92" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" s="11" t="s">
         <v>240</v>
       </c>
@@ -6347,7 +6360,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" s="61" t="s">
         <v>77</v>
       </c>
@@ -6392,7 +6405,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="94" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" s="11" t="s">
         <v>80</v>
       </c>
@@ -6437,7 +6450,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="95" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" s="38" t="s">
         <v>205</v>
       </c>
@@ -6480,7 +6493,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="96" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" s="71" t="s">
         <v>81</v>
       </c>
@@ -6525,7 +6538,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A97" s="38" t="s">
         <v>119</v>
       </c>
@@ -6570,7 +6583,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A98" s="63" t="s">
         <v>120</v>
       </c>
@@ -6615,7 +6628,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A99" s="20" t="s">
         <v>160</v>
       </c>
@@ -6660,7 +6673,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A100" s="11" t="s">
         <v>121</v>
       </c>
@@ -6705,7 +6718,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A101" s="23" t="s">
         <v>232</v>
       </c>
@@ -6750,7 +6763,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A102" s="11" t="s">
         <v>277</v>
       </c>
@@ -6795,7 +6808,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="11" t="s">
         <v>265</v>
       </c>
@@ -6826,7 +6839,7 @@
       </c>
       <c r="M103" s="6"/>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="23" t="s">
         <v>244</v>
       </c>
@@ -6871,7 +6884,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="61" t="s">
         <v>246</v>
       </c>
@@ -6916,7 +6929,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="106" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="11" t="s">
         <v>186</v>
       </c>
@@ -6961,7 +6974,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="23" t="s">
         <v>292</v>
       </c>
@@ -7006,7 +7019,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="20" t="s">
         <v>228</v>
       </c>
@@ -7051,7 +7064,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="20" t="s">
         <v>123</v>
       </c>
@@ -7096,7 +7109,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="20" t="s">
         <v>160</v>
       </c>
@@ -7141,7 +7154,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="11" t="s">
         <v>212</v>
       </c>
@@ -7186,7 +7199,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="112" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="20" t="s">
         <v>297</v>
       </c>
@@ -7231,7 +7244,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A113" s="11" t="s">
         <v>36</v>
       </c>
@@ -7277,7 +7290,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A114" s="20" t="s">
         <v>225</v>
       </c>
@@ -7322,7 +7335,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A115" s="11" t="s">
         <v>272</v>
       </c>
@@ -7367,7 +7380,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A116" s="23" t="s">
         <v>245</v>
       </c>
@@ -7412,7 +7425,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A117" s="11" t="s">
         <v>169</v>
       </c>
@@ -7457,7 +7470,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="118" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A118" s="23" t="s">
         <v>160</v>
       </c>
@@ -7502,7 +7515,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A119" s="11" t="s">
         <v>232</v>
       </c>
@@ -7547,7 +7560,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="120" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A120" s="20" t="s">
         <v>292</v>
       </c>
@@ -7592,7 +7605,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A121" s="38" t="s">
         <v>205</v>
       </c>
@@ -7637,7 +7650,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A122" s="23" t="s">
         <v>213</v>
       </c>
@@ -7682,7 +7695,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="123" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A123" s="11" t="s">
         <v>213</v>
       </c>
@@ -7727,7 +7740,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A124" s="20" t="s">
         <v>300</v>
       </c>
@@ -7772,7 +7785,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A125" s="11" t="s">
         <v>302</v>
       </c>
@@ -7817,7 +7830,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A126" s="23" t="s">
         <v>36</v>
       </c>
@@ -7862,7 +7875,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="127" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A127" s="11" t="s">
         <v>154</v>
       </c>
@@ -7907,7 +7920,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="128" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A128" s="23" t="s">
         <v>262</v>
       </c>
@@ -7952,7 +7965,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A129" s="11" t="s">
         <v>292</v>
       </c>
@@ -7997,7 +8010,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A130" s="11" t="s">
         <v>244</v>
       </c>
@@ -8042,7 +8055,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A131" s="20" t="s">
         <v>147</v>
       </c>
@@ -8087,7 +8100,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A132" s="23" t="s">
         <v>70</v>
       </c>
@@ -8129,7 +8142,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A133" s="69" t="s">
         <v>81</v>
       </c>
@@ -8170,7 +8183,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="134" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A134" s="23" t="s">
         <v>113</v>
       </c>
@@ -8211,7 +8224,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="135" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A135" s="11" t="s">
         <v>41</v>
       </c>
@@ -8256,7 +8269,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A136" s="11" t="s">
         <v>42</v>
       </c>
@@ -8295,7 +8308,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A137" s="23" t="s">
         <v>82</v>
       </c>
@@ -8338,7 +8351,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="138" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A138" s="11" t="s">
         <v>42</v>
       </c>
@@ -8383,7 +8396,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="139" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A139" s="20" t="s">
         <v>46</v>
       </c>
@@ -8428,7 +8441,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A140" s="11" t="s">
         <v>46</v>
       </c>
@@ -8473,7 +8486,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A141" s="23" t="s">
         <v>49</v>
       </c>
@@ -8519,7 +8532,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="142" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A142" s="11" t="s">
         <v>49</v>
       </c>
@@ -8564,7 +8577,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="143" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A143" s="63" t="s">
         <v>49</v>
       </c>
@@ -8609,7 +8622,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="144" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A144" s="23" t="s">
         <v>52</v>
       </c>
@@ -8654,7 +8667,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="145" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A145" s="23" t="s">
         <v>52</v>
       </c>
@@ -8691,7 +8704,7 @@
       </c>
       <c r="M145" s="6"/>
     </row>
-    <row r="146" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A146" s="23" t="s">
         <v>52</v>
       </c>
@@ -8737,7 +8750,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="147" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A147" s="11" t="s">
         <v>157</v>
       </c>
@@ -8782,7 +8795,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="148" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A148" s="20" t="s">
         <v>52</v>
       </c>
@@ -8827,7 +8840,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="149" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A149" s="70" t="s">
         <v>52</v>
       </c>
@@ -8864,7 +8877,7 @@
       </c>
       <c r="M149" s="6"/>
     </row>
-    <row r="150" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A150" s="20" t="s">
         <v>57</v>
       </c>
@@ -8909,7 +8922,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A151" s="11" t="s">
         <v>57</v>
       </c>
@@ -8954,7 +8967,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A152" s="70" t="s">
         <v>65</v>
       </c>
@@ -8999,7 +9012,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="153" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A153" s="71" t="s">
         <v>65</v>
       </c>
@@ -9044,7 +9057,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="154" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A154" s="70" t="s">
         <v>65</v>
       </c>
@@ -9089,7 +9102,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="155" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A155" s="20" t="s">
         <v>70</v>
       </c>
@@ -9134,7 +9147,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="156" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A156" s="20" t="s">
         <v>222</v>
       </c>
@@ -9179,7 +9192,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="157" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A157" s="23" t="s">
         <v>228</v>
       </c>
@@ -9224,7 +9237,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="158" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A158" s="38" t="s">
         <v>70</v>
       </c>
@@ -9269,7 +9282,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="159" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A159" s="23" t="s">
         <v>210</v>
       </c>
@@ -9315,7 +9328,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="160" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A160" s="69" t="s">
         <v>73</v>
       </c>
@@ -9360,7 +9373,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="161" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A161" s="11" t="s">
         <v>302</v>
       </c>
@@ -9405,7 +9418,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="162" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A162" s="20" t="s">
         <v>144</v>
       </c>
@@ -9450,7 +9463,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="163" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A163" s="23" t="s">
         <v>212</v>
       </c>
@@ -9495,7 +9508,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="164" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A164" s="20" t="s">
         <v>262</v>
       </c>
@@ -9540,7 +9553,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A165" s="70" t="s">
         <v>73</v>
       </c>
@@ -9585,7 +9598,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="166" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A166" s="11" t="s">
         <v>170</v>
       </c>
@@ -9630,7 +9643,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="167" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A167" s="20" t="s">
         <v>147</v>
       </c>
@@ -9675,7 +9688,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="168" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A168" s="11" t="s">
         <v>74</v>
       </c>
@@ -9716,7 +9729,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="169" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A169" s="36" t="s">
         <v>253</v>
       </c>
@@ -9762,7 +9775,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="170" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A170" s="70" t="s">
         <v>76</v>
       </c>
@@ -9852,7 +9865,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A172" s="11" t="s">
         <v>300</v>
       </c>
@@ -9897,7 +9910,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="173" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A173" s="36" t="s">
         <v>199</v>
       </c>
@@ -9940,7 +9953,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A174" s="36" t="s">
         <v>253</v>
       </c>
@@ -9985,7 +9998,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A175" s="23" t="s">
         <v>297</v>
       </c>
@@ -10028,7 +10041,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A176" s="11" t="s">
         <v>240</v>
       </c>
@@ -10073,7 +10086,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A177" s="71" t="s">
         <v>76</v>
       </c>
@@ -10118,7 +10131,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A178" s="20" t="s">
         <v>77</v>
       </c>
@@ -10163,7 +10176,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A179" s="11" t="s">
         <v>77</v>
       </c>
@@ -10208,7 +10221,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A180" s="23" t="s">
         <v>80</v>
       </c>
@@ -10253,7 +10266,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A181" s="20" t="s">
         <v>80</v>
       </c>
@@ -10298,7 +10311,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A182" s="23" t="s">
         <v>80</v>
       </c>
@@ -10343,7 +10356,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A183" s="70" t="s">
         <v>80</v>
       </c>
@@ -10380,7 +10393,7 @@
       </c>
       <c r="M183" s="6"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A184" s="70" t="s">
         <v>81</v>
       </c>
@@ -10425,7 +10438,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A185" s="70" t="s">
         <v>81</v>
       </c>
@@ -10470,7 +10483,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A186" s="71" t="s">
         <v>81</v>
       </c>
@@ -10515,7 +10528,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A187" s="70" t="s">
         <v>81</v>
       </c>
@@ -10560,7 +10573,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A188" s="70" t="s">
         <v>81</v>
       </c>
@@ -10597,7 +10610,7 @@
       </c>
       <c r="M188" s="6"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A189" s="11" t="s">
         <v>82</v>
       </c>
@@ -10642,7 +10655,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A190" s="23" t="s">
         <v>82</v>
       </c>
@@ -10687,7 +10700,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A191" s="70" t="s">
         <v>82</v>
       </c>
@@ -10724,7 +10737,7 @@
       </c>
       <c r="M191" s="6"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A192" s="11" t="s">
         <v>86</v>
       </c>
@@ -10769,7 +10782,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A193" s="20" t="s">
         <v>87</v>
       </c>
@@ -10814,7 +10827,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A194" s="38" t="s">
         <v>205</v>
       </c>
@@ -10859,7 +10872,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="195" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A195" s="20" t="s">
         <v>222</v>
       </c>
@@ -10904,7 +10917,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A196" s="20" t="s">
         <v>225</v>
       </c>
@@ -10949,7 +10962,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A197" s="61" t="s">
         <v>246</v>
       </c>
@@ -10994,7 +11007,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A198" s="11" t="s">
         <v>289</v>
       </c>
@@ -11039,7 +11052,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A199" s="23" t="s">
         <v>294</v>
       </c>
@@ -11084,7 +11097,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A200" s="38" t="s">
         <v>205</v>
       </c>
@@ -11129,7 +11142,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A201" s="23" t="s">
         <v>230</v>
       </c>
@@ -11174,7 +11187,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A202" s="70" t="s">
         <v>11</v>
       </c>
@@ -11219,7 +11232,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A203" s="23" t="s">
         <v>46</v>
       </c>
@@ -11264,7 +11277,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A204" s="11" t="s">
         <v>192</v>
       </c>
@@ -11309,7 +11322,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A205" s="63" t="s">
         <v>205</v>
       </c>
@@ -11354,7 +11367,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A206" s="11" t="s">
         <v>170</v>
       </c>
@@ -11399,7 +11412,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A207" s="36" t="s">
         <v>199</v>
       </c>
@@ -11445,7 +11458,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A208" s="11" t="s">
         <v>245</v>
       </c>
@@ -11490,7 +11503,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A209" s="20" t="s">
         <v>155</v>
       </c>
@@ -11535,7 +11548,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A210" s="36" t="s">
         <v>199</v>
       </c>
@@ -11581,7 +11594,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="211" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A211" s="11" t="s">
         <v>286</v>
       </c>
@@ -11626,7 +11639,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A212" s="20" t="s">
         <v>287</v>
       </c>
@@ -11671,7 +11684,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A213" s="11" t="s">
         <v>243</v>
       </c>
@@ -11716,7 +11729,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A214" s="11" t="s">
         <v>89</v>
       </c>
@@ -11761,7 +11774,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A215" s="23" t="s">
         <v>87</v>
       </c>
@@ -11806,7 +11819,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A216" s="11" t="s">
         <v>88</v>
       </c>
@@ -11851,7 +11864,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A217" s="11" t="s">
         <v>88</v>
       </c>
@@ -11894,7 +11907,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A218" s="20" t="s">
         <v>289</v>
       </c>
@@ -11939,7 +11952,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="219" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A219" s="11" t="s">
         <v>160</v>
       </c>
@@ -11984,7 +11997,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A220" s="20" t="s">
         <v>192</v>
       </c>
@@ -12029,7 +12042,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A221" s="11" t="s">
         <v>240</v>
       </c>
@@ -12074,7 +12087,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A222" s="20" t="s">
         <v>281</v>
       </c>
@@ -12119,7 +12132,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A223" s="11" t="s">
         <v>282</v>
       </c>
@@ -12164,7 +12177,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A224" s="23" t="s">
         <v>294</v>
       </c>
@@ -12209,7 +12222,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A225" s="11" t="s">
         <v>228</v>
       </c>
@@ -12254,7 +12267,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A226" s="23" t="s">
         <v>88</v>
       </c>
@@ -12299,7 +12312,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A227" s="23" t="s">
         <v>186</v>
       </c>
@@ -12344,7 +12357,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A228" s="11" t="s">
         <v>300</v>
       </c>
@@ -12389,7 +12402,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A229" s="61" t="s">
         <v>205</v>
       </c>
@@ -12434,7 +12447,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A230" s="11" t="s">
         <v>225</v>
       </c>
@@ -12479,7 +12492,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A231" s="23" t="s">
         <v>213</v>
       </c>
@@ -12524,7 +12537,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A232" s="61" t="s">
         <v>246</v>
       </c>
@@ -12559,7 +12572,7 @@
         <v>0</v>
       </c>
       <c r="K232" s="26" t="str">
-        <f t="shared" ref="K232:K263" si="27">IF(E232=0,"Sin Plan",IF(J232&gt;=1,"Completado",IF(J232&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
+        <f t="shared" ref="K232:K240" si="27">IF(E232=0,"Sin Plan",IF(J232&gt;=1,"Completado",IF(J232&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
         <v>Sin Plan</v>
       </c>
       <c r="L232" s="6" t="s">
@@ -12569,7 +12582,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A233" s="36" t="s">
         <v>199</v>
       </c>
@@ -12614,7 +12627,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A234" s="11" t="s">
         <v>245</v>
       </c>
@@ -12659,7 +12672,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A235" s="23" t="s">
         <v>287</v>
       </c>
@@ -12704,7 +12717,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A236" s="11" t="s">
         <v>300</v>
       </c>
@@ -12749,7 +12762,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A237" s="23" t="s">
         <v>302</v>
       </c>
@@ -12794,7 +12807,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A238" s="11" t="s">
         <v>125</v>
       </c>
@@ -12839,7 +12852,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A239" s="20" t="s">
         <v>88</v>
       </c>
@@ -12884,7 +12897,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A240" s="11" t="s">
         <v>225</v>
       </c>
@@ -12929,7 +12942,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A241" s="11" t="s">
         <v>258</v>
       </c>
@@ -12960,7 +12973,7 @@
       </c>
       <c r="M241" s="6"/>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A242" s="23" t="s">
         <v>225</v>
       </c>
@@ -13003,7 +13016,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A243" s="38" t="s">
         <v>205</v>
       </c>
@@ -13049,7 +13062,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A244" s="20" t="s">
         <v>147</v>
       </c>
@@ -13094,7 +13107,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A245" s="11" t="s">
         <v>222</v>
       </c>
@@ -13139,7 +13152,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A246" s="23" t="s">
         <v>155</v>
       </c>
@@ -13185,7 +13198,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A247" s="11" t="s">
         <v>229</v>
       </c>
@@ -13230,7 +13243,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="248" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A248" s="20" t="s">
         <v>262</v>
       </c>
@@ -13273,7 +13286,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A249" s="23" t="s">
         <v>89</v>
       </c>
@@ -13318,7 +13331,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A250" s="11" t="s">
         <v>89</v>
       </c>
@@ -13363,7 +13376,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="251" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A251" s="20" t="s">
         <v>160</v>
       </c>
@@ -13408,7 +13421,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="252" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A252" s="11" t="s">
         <v>169</v>
       </c>
@@ -13453,7 +13466,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="253" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A253" s="11" t="s">
         <v>229</v>
       </c>
@@ -13498,7 +13511,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="254" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A254" s="23" t="s">
         <v>272</v>
       </c>
@@ -13543,7 +13556,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="255" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A255" s="70" t="s">
         <v>11</v>
       </c>
@@ -13588,7 +13601,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="256" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A256" s="11" t="s">
         <v>89</v>
       </c>
@@ -13633,7 +13646,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="257" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A257" s="20" t="s">
         <v>89</v>
       </c>
@@ -13678,7 +13691,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="258" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A258" s="11" t="s">
         <v>89</v>
       </c>
@@ -13723,7 +13736,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="259" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A259" s="11" t="s">
         <v>94</v>
       </c>
@@ -13768,7 +13781,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="260" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A260" s="23" t="s">
         <v>225</v>
       </c>
@@ -13813,7 +13826,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="261" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A261" s="23" t="s">
         <v>94</v>
       </c>
@@ -13858,7 +13871,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="262" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A262" s="11" t="s">
         <v>104</v>
       </c>
@@ -13903,7 +13916,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="263" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A263" s="23" t="s">
         <v>57</v>
       </c>
@@ -13948,7 +13961,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="264" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A264" s="23" t="s">
         <v>240</v>
       </c>
@@ -13993,7 +14006,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="265" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A265" s="20" t="s">
         <v>262</v>
       </c>
@@ -14038,7 +14051,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="266" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A266" s="11" t="s">
         <v>202</v>
       </c>
@@ -14083,7 +14096,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="267" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A267" s="20" t="s">
         <v>303</v>
       </c>
@@ -14128,7 +14141,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="268" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A268" s="11" t="s">
         <v>283</v>
       </c>
@@ -14173,7 +14186,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="269" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A269" s="70" t="s">
         <v>73</v>
       </c>
@@ -14218,7 +14231,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="270" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A270" s="61" t="s">
         <v>76</v>
       </c>
@@ -14263,7 +14276,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="271" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A271" s="11" t="s">
         <v>89</v>
       </c>
@@ -14308,7 +14321,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="272" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A272" s="11" t="s">
         <v>70</v>
       </c>
@@ -14353,7 +14366,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="273" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A273" s="11" t="s">
         <v>52</v>
       </c>
@@ -14398,7 +14411,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="274" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A274" s="11" t="s">
         <v>186</v>
       </c>
@@ -14443,7 +14456,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="275" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A275" s="23" t="s">
         <v>186</v>
       </c>
@@ -14488,7 +14501,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="276" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A276" s="11" t="s">
         <v>186</v>
       </c>
@@ -14533,7 +14546,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="277" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A277" s="20" t="s">
         <v>212</v>
       </c>
@@ -14578,7 +14591,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="278" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A278" s="11" t="s">
         <v>265</v>
       </c>
@@ -14623,7 +14636,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="279" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A279" s="20" t="s">
         <v>265</v>
       </c>
@@ -14668,7 +14681,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="280" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A280" s="11" t="s">
         <v>300</v>
       </c>
@@ -14713,7 +14726,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="281" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A281" s="38" t="s">
         <v>41</v>
       </c>
@@ -14758,7 +14771,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="282" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A282" s="11" t="s">
         <v>232</v>
       </c>
@@ -14803,7 +14816,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="283" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A283" s="23" t="s">
         <v>294</v>
       </c>
@@ -14848,7 +14861,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="284" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A284" s="23" t="s">
         <v>262</v>
       </c>
@@ -14893,7 +14906,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="285" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A285" s="23" t="s">
         <v>289</v>
       </c>
@@ -14938,7 +14951,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="286" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A286" s="11" t="s">
         <v>289</v>
       </c>
@@ -14983,7 +14996,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="287" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A287" s="23" t="s">
         <v>243</v>
       </c>
@@ -15028,7 +15041,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="288" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A288" s="11" t="s">
         <v>302</v>
       </c>
@@ -15073,7 +15086,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="289" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A289" s="23" t="s">
         <v>202</v>
       </c>
@@ -15118,7 +15131,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="290" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A290" s="23" t="s">
         <v>86</v>
       </c>
@@ -15163,7 +15176,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="291" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A291" s="36" t="s">
         <v>199</v>
       </c>
@@ -15206,7 +15219,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="292" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A292" s="11" t="s">
         <v>300</v>
       </c>
@@ -15251,7 +15264,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="293" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A293" s="20" t="s">
         <v>302</v>
       </c>
@@ -15296,7 +15309,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="294" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A294" s="38" t="s">
         <v>205</v>
       </c>
@@ -15341,7 +15354,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="295" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A295" s="11" t="s">
         <v>87</v>
       </c>
@@ -15386,7 +15399,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="296" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A296" s="11" t="s">
         <v>169</v>
       </c>
@@ -15431,7 +15444,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="297" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A297" s="23" t="s">
         <v>98</v>
       </c>
@@ -15477,7 +15490,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="298" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A298" s="11" t="s">
         <v>302</v>
       </c>
@@ -15522,7 +15535,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="299" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A299" s="11" t="s">
         <v>116</v>
       </c>
@@ -15567,7 +15580,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="300" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A300" s="11" t="s">
         <v>294</v>
       </c>
@@ -15612,7 +15625,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="301" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A301" s="63" t="s">
         <v>205</v>
       </c>
@@ -15657,7 +15670,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="302" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A302" s="11" t="s">
         <v>128</v>
       </c>
@@ -15702,7 +15715,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A303" s="23" t="s">
         <v>154</v>
       </c>
@@ -15747,7 +15760,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="304" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A304" s="70" t="s">
         <v>11</v>
       </c>
@@ -15792,7 +15805,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A305" s="23" t="s">
         <v>228</v>
       </c>
@@ -15837,7 +15850,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A306" s="11" t="s">
         <v>230</v>
       </c>
@@ -15880,7 +15893,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A307" s="23" t="s">
         <v>186</v>
       </c>
@@ -15925,7 +15938,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A308" s="11" t="s">
         <v>106</v>
       </c>
@@ -15964,7 +15977,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A309" s="20" t="s">
         <v>111</v>
       </c>
@@ -16003,7 +16016,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A310" s="20" t="s">
         <v>52</v>
       </c>
@@ -16048,7 +16061,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A311" s="11" t="s">
         <v>82</v>
       </c>
@@ -16093,7 +16106,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A312" s="11" t="s">
         <v>94</v>
       </c>
@@ -16138,7 +16151,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A313" s="11" t="s">
         <v>42</v>
       </c>
@@ -16183,7 +16196,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A314" s="11" t="s">
         <v>109</v>
       </c>
@@ -16228,7 +16241,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A315" s="11" t="s">
         <v>87</v>
       </c>
@@ -16271,7 +16284,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A316" s="11" t="s">
         <v>114</v>
       </c>
@@ -16314,7 +16327,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A317" s="23" t="s">
         <v>94</v>
       </c>
@@ -16359,7 +16372,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A318" s="63" t="s">
         <v>121</v>
       </c>
@@ -16404,7 +16417,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A319" s="11" t="s">
         <v>36</v>
       </c>
@@ -16449,7 +16462,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A320" s="20" t="s">
         <v>116</v>
       </c>
@@ -16494,7 +16507,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A321" s="20" t="s">
         <v>262</v>
       </c>
@@ -16539,7 +16552,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A322" s="63" t="s">
         <v>86</v>
       </c>
@@ -16584,7 +16597,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A323" s="20" t="s">
         <v>192</v>
       </c>
@@ -16629,7 +16642,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A324" s="23" t="s">
         <v>202</v>
       </c>
@@ -16674,7 +16687,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A325" s="11" t="s">
         <v>229</v>
       </c>
@@ -16719,7 +16732,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A326" s="11" t="s">
         <v>288</v>
       </c>
@@ -16764,7 +16777,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="327" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A327" s="20" t="s">
         <v>299</v>
       </c>
@@ -16809,7 +16822,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="328" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A328" s="11" t="s">
         <v>106</v>
       </c>
@@ -16854,7 +16867,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="329" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A329" s="20" t="s">
         <v>222</v>
       </c>
@@ -16899,7 +16912,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="330" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A330" s="11" t="s">
         <v>245</v>
       </c>
@@ -16944,7 +16957,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="331" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A331" s="23" t="s">
         <v>111</v>
       </c>
@@ -16989,7 +17002,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="332" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A332" s="11" t="s">
         <v>94</v>
       </c>
@@ -17034,7 +17047,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="333" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A333" s="23" t="s">
         <v>94</v>
       </c>
@@ -17079,7 +17092,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="334" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A334" s="11" t="s">
         <v>94</v>
       </c>
@@ -17124,7 +17137,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="335" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A335" s="11" t="s">
         <v>98</v>
       </c>
@@ -17167,7 +17180,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="336" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A336" s="23" t="s">
         <v>98</v>
       </c>
@@ -17212,7 +17225,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="337" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A337" s="20" t="s">
         <v>170</v>
       </c>
@@ -17257,7 +17270,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="338" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A338" s="63" t="s">
         <v>205</v>
       </c>
@@ -17292,7 +17305,7 @@
         <v>1.9573392857142857</v>
       </c>
       <c r="K338" s="22" t="str">
-        <f t="shared" ref="K338:K369" si="39">IF(E338=0,"Sin Plan",IF(J338&gt;=1,"Completado",IF(J338&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
+        <f t="shared" ref="K338:K344" si="39">IF(E338=0,"Sin Plan",IF(J338&gt;=1,"Completado",IF(J338&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
         <v>Completado</v>
       </c>
       <c r="L338" s="6" t="s">
@@ -17302,7 +17315,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="339" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A339" s="11" t="s">
         <v>212</v>
       </c>
@@ -17347,7 +17360,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="340" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A340" s="11" t="s">
         <v>303</v>
       </c>
@@ -17392,7 +17405,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="341" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A341" s="20" t="s">
         <v>292</v>
       </c>
@@ -17437,7 +17450,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="342" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A342" s="11" t="s">
         <v>98</v>
       </c>
@@ -17480,7 +17493,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="343" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A343" s="20" t="s">
         <v>98</v>
       </c>
@@ -17525,7 +17538,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="344" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A344" s="70" t="s">
         <v>98</v>
       </c>
@@ -17562,7 +17575,7 @@
       </c>
       <c r="M344" s="6"/>
     </row>
-    <row r="345" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A345" s="61" t="s">
         <v>246</v>
       </c>
@@ -17593,7 +17606,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="346" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A346" s="23" t="s">
         <v>262</v>
       </c>
@@ -17638,7 +17651,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="347" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A347" s="20" t="s">
         <v>294</v>
       </c>
@@ -17683,7 +17696,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="348" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A348" s="11" t="s">
         <v>258</v>
       </c>
@@ -17728,7 +17741,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="349" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A349" s="20" t="s">
         <v>104</v>
       </c>
@@ -17773,7 +17786,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="350" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A350" s="11" t="s">
         <v>186</v>
       </c>
@@ -17818,7 +17831,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="351" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A351" s="23" t="s">
         <v>212</v>
       </c>
@@ -17863,7 +17876,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="352" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A352" s="11" t="s">
         <v>104</v>
       </c>
@@ -17908,7 +17921,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="353" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A353" s="11" t="s">
         <v>104</v>
       </c>
@@ -17953,7 +17966,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="354" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A354" s="23" t="s">
         <v>104</v>
       </c>
@@ -17998,7 +18011,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="355" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A355" s="20" t="s">
         <v>105</v>
       </c>
@@ -18043,7 +18056,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="356" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A356" s="11" t="s">
         <v>106</v>
       </c>
@@ -18088,7 +18101,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="357" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A357" s="23" t="s">
         <v>229</v>
       </c>
@@ -18133,7 +18146,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="358" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A358" s="20" t="s">
         <v>106</v>
       </c>
@@ -18178,7 +18191,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="359" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A359" s="23" t="s">
         <v>169</v>
       </c>
@@ -18222,7 +18235,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="360" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A360" s="11" t="s">
         <v>186</v>
       </c>
@@ -18267,7 +18280,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="361" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A361" s="20" t="s">
         <v>297</v>
       </c>
@@ -18312,7 +18325,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="362" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A362" s="23" t="s">
         <v>106</v>
       </c>
@@ -18357,7 +18370,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="363" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A363" s="61" t="s">
         <v>246</v>
       </c>
@@ -18403,7 +18416,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="364" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A364" s="11" t="s">
         <v>106</v>
       </c>
@@ -18446,7 +18459,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="365" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A365" s="20" t="s">
         <v>212</v>
       </c>
@@ -18491,7 +18504,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="366" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A366" s="11" t="s">
         <v>186</v>
       </c>
@@ -18536,7 +18549,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="367" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A367" s="23" t="s">
         <v>261</v>
       </c>
@@ -18581,7 +18594,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="368" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A368" s="11" t="s">
         <v>265</v>
       </c>
@@ -18624,7 +18637,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="369" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A369" s="23" t="s">
         <v>297</v>
       </c>
@@ -18669,7 +18682,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="370" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A370" s="20" t="s">
         <v>262</v>
       </c>
@@ -18714,7 +18727,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="371" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A371" s="23" t="s">
         <v>292</v>
       </c>
@@ -18759,7 +18772,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="372" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A372" s="11" t="s">
         <v>302</v>
       </c>
@@ -18802,7 +18815,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="373" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A373" s="20" t="s">
         <v>213</v>
       </c>
@@ -18847,7 +18860,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="374" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A374" s="11" t="s">
         <v>231</v>
       </c>
@@ -18890,7 +18903,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="375" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A375" s="70" t="s">
         <v>106</v>
       </c>
@@ -18927,7 +18940,7 @@
       </c>
       <c r="M375" s="6"/>
     </row>
-    <row r="376" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A376" s="11" t="s">
         <v>109</v>
       </c>
@@ -18972,7 +18985,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="377" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A377" s="20" t="s">
         <v>110</v>
       </c>
@@ -19017,7 +19030,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="378" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A378" s="23" t="s">
         <v>110</v>
       </c>
@@ -19052,7 +19065,7 @@
         <v>1.0853289682539684</v>
       </c>
       <c r="K378" s="26" t="str">
-        <f t="shared" ref="K378:K409" si="43">IF(E378=0,"Sin Plan",IF(J378&gt;=1,"Completado",IF(J378&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
+        <f t="shared" ref="K378:K407" si="43">IF(E378=0,"Sin Plan",IF(J378&gt;=1,"Completado",IF(J378&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
         <v>Completado</v>
       </c>
       <c r="L378" s="6" t="s">
@@ -19062,7 +19075,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="379" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A379" s="11" t="s">
         <v>110</v>
       </c>
@@ -19107,7 +19120,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="380" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A380" s="20" t="s">
         <v>111</v>
       </c>
@@ -19152,7 +19165,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="381" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A381" s="23" t="s">
         <v>111</v>
       </c>
@@ -19197,7 +19210,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="382" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A382" s="70" t="s">
         <v>111</v>
       </c>
@@ -19234,7 +19247,7 @@
       </c>
       <c r="M382" s="6"/>
     </row>
-    <row r="383" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A383" s="23" t="s">
         <v>112</v>
       </c>
@@ -19279,7 +19292,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="384" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A384" s="11" t="s">
         <v>112</v>
       </c>
@@ -19324,7 +19337,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="385" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A385" s="11" t="s">
         <v>112</v>
       </c>
@@ -19369,7 +19382,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="386" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A386" s="11" t="s">
         <v>213</v>
       </c>
@@ -19414,7 +19427,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="387" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A387" s="23" t="s">
         <v>262</v>
       </c>
@@ -19459,7 +19472,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="388" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A388" s="11" t="s">
         <v>245</v>
       </c>
@@ -19504,7 +19517,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="389" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A389" s="11" t="s">
         <v>112</v>
       </c>
@@ -19549,7 +19562,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="390" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A390" s="23" t="s">
         <v>245</v>
       </c>
@@ -19594,7 +19607,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="391" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A391" s="61" t="s">
         <v>246</v>
       </c>
@@ -19639,7 +19652,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="392" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A392" s="38" t="s">
         <v>205</v>
       </c>
@@ -19684,7 +19697,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="393" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A393" s="20" t="s">
         <v>289</v>
       </c>
@@ -19729,7 +19742,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="394" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A394" s="11" t="s">
         <v>212</v>
       </c>
@@ -19774,7 +19787,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="395" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A395" s="20" t="s">
         <v>266</v>
       </c>
@@ -19819,7 +19832,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="396" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A396" s="38" t="s">
         <v>112</v>
       </c>
@@ -19864,7 +19877,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="397" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A397" s="70" t="s">
         <v>112</v>
       </c>
@@ -19901,7 +19914,7 @@
       </c>
       <c r="M397" s="6"/>
     </row>
-    <row r="398" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A398" s="11" t="s">
         <v>245</v>
       </c>
@@ -19946,7 +19959,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="399" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A399" s="23" t="s">
         <v>113</v>
       </c>
@@ -19991,7 +20004,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="400" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A400" s="11" t="s">
         <v>222</v>
       </c>
@@ -20036,7 +20049,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="401" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A401" s="20" t="s">
         <v>113</v>
       </c>
@@ -20081,7 +20094,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="402" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A402" s="11" t="s">
         <v>113</v>
       </c>
@@ -20126,7 +20139,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="403" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A403" s="20" t="s">
         <v>114</v>
       </c>
@@ -20169,7 +20182,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="404" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A404" s="11" t="s">
         <v>160</v>
       </c>
@@ -20214,7 +20227,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="405" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A405" s="23" t="s">
         <v>262</v>
       </c>
@@ -20259,7 +20272,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="406" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A406" s="11" t="s">
         <v>210</v>
       </c>
@@ -20304,7 +20317,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="407" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A407" s="11" t="s">
         <v>114</v>
       </c>
@@ -20347,7 +20360,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="408" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A408" s="20" t="s">
         <v>202</v>
       </c>
@@ -20378,7 +20391,7 @@
       </c>
       <c r="M408" s="6"/>
     </row>
-    <row r="409" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A409" s="20" t="s">
         <v>114</v>
       </c>
@@ -20419,7 +20432,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="410" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A410" s="70" t="s">
         <v>114</v>
       </c>
@@ -20456,7 +20469,7 @@
       </c>
       <c r="M410" s="6"/>
     </row>
-    <row r="411" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A411" s="11" t="s">
         <v>202</v>
       </c>
@@ -20501,7 +20514,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="412" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A412" s="23" t="s">
         <v>299</v>
       </c>
@@ -20546,7 +20559,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="413" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A413" s="11" t="s">
         <v>305</v>
       </c>
@@ -20591,7 +20604,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="414" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A414" s="20" t="s">
         <v>169</v>
       </c>
@@ -20636,7 +20649,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="415" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A415" s="23" t="s">
         <v>210</v>
       </c>
@@ -20681,7 +20694,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="416" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A416" s="11" t="s">
         <v>229</v>
       </c>
@@ -20726,7 +20739,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="417" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A417" s="11" t="s">
         <v>213</v>
       </c>
@@ -20771,7 +20784,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="418" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A418" s="20" t="s">
         <v>225</v>
       </c>
@@ -20816,7 +20829,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="419" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A419" s="11" t="s">
         <v>243</v>
       </c>
@@ -20861,7 +20874,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="420" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A420" s="36" t="s">
         <v>253</v>
       </c>
@@ -20906,7 +20919,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="421" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A421" s="11" t="s">
         <v>258</v>
       </c>
@@ -20951,7 +20964,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="422" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A422" s="23" t="s">
         <v>288</v>
       </c>
@@ -20996,7 +21009,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="423" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A423" s="11" t="s">
         <v>303</v>
       </c>
@@ -21041,7 +21054,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="424" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A424" s="20" t="s">
         <v>245</v>
       </c>
@@ -21086,7 +21099,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="425" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A425" s="11" t="s">
         <v>210</v>
       </c>
@@ -21131,7 +21144,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="426" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A426" s="20" t="s">
         <v>212</v>
       </c>
@@ -21176,7 +21189,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="427" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A427" s="11" t="s">
         <v>244</v>
       </c>
@@ -21221,7 +21234,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="428" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A428" s="23" t="s">
         <v>116</v>
       </c>
@@ -21266,7 +21279,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="429" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A429" s="11" t="s">
         <v>117</v>
       </c>
@@ -21311,7 +21324,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="430" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A430" s="20" t="s">
         <v>117</v>
       </c>
@@ -21356,7 +21369,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="431" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A431" s="11" t="s">
         <v>117</v>
       </c>
@@ -21401,7 +21414,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="432" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A432" s="70" t="s">
         <v>117</v>
       </c>
@@ -21438,7 +21451,7 @@
       </c>
       <c r="M432" s="6"/>
     </row>
-    <row r="433" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A433" s="23" t="s">
         <v>114</v>
       </c>
@@ -21477,7 +21490,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="434" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A434" s="11" t="s">
         <v>98</v>
       </c>
@@ -21516,7 +21529,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="435" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A435" s="38" t="s">
         <v>57</v>
       </c>
@@ -21561,7 +21574,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="436" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A436" s="11" t="s">
         <v>62</v>
       </c>
@@ -21605,7 +21618,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="437" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A437" s="11" t="s">
         <v>118</v>
       </c>
@@ -21650,7 +21663,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="438" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A438" s="23" t="s">
         <v>118</v>
       </c>
@@ -21695,7 +21708,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="439" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A439" s="38" t="s">
         <v>104</v>
       </c>
@@ -21740,7 +21753,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="440" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A440" s="61" t="s">
         <v>70</v>
       </c>
@@ -21785,7 +21798,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="441" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A441" s="38" t="s">
         <v>36</v>
       </c>
@@ -21830,7 +21843,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="442" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A442" s="61" t="s">
         <v>41</v>
       </c>
@@ -21875,7 +21888,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="443" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A443" s="38" t="s">
         <v>46</v>
       </c>
@@ -21920,7 +21933,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="444" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A444" s="63" t="s">
         <v>52</v>
       </c>
@@ -21965,7 +21978,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="445" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A445" s="38" t="s">
         <v>57</v>
       </c>
@@ -22010,7 +22023,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="446" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A446" s="69" t="s">
         <v>11</v>
       </c>
@@ -22055,7 +22068,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="447" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A447" s="63" t="s">
         <v>35</v>
       </c>
@@ -22100,7 +22113,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="448" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A448" s="23" t="s">
         <v>35</v>
       </c>
@@ -22145,7 +22158,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="449" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A449" s="11" t="s">
         <v>41</v>
       </c>
@@ -22190,7 +22203,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="450" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A450" s="20" t="s">
         <v>46</v>
       </c>
@@ -22235,7 +22248,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="451" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A451" s="11" t="s">
         <v>74</v>
       </c>
@@ -22280,7 +22293,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="452" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A452" s="23" t="s">
         <v>82</v>
       </c>
@@ -22325,7 +22338,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="453" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A453" s="11" t="s">
         <v>87</v>
       </c>
@@ -22370,7 +22383,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="454" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A454" s="61" t="s">
         <v>89</v>
       </c>
@@ -22415,7 +22428,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="455" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A455" s="38" t="s">
         <v>94</v>
       </c>
@@ -22460,7 +22473,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="456" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A456" s="61" t="s">
         <v>109</v>
       </c>
@@ -22505,7 +22518,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="457" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A457" s="11" t="s">
         <v>110</v>
       </c>
@@ -22550,7 +22563,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="458" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A458" s="20" t="s">
         <v>111</v>
       </c>
@@ -22595,7 +22608,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="459" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A459" s="11" t="s">
         <v>112</v>
       </c>
@@ -22640,7 +22653,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="460" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A460" s="20" t="s">
         <v>128</v>
       </c>
@@ -22685,7 +22698,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="461" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A461" s="20" t="s">
         <v>128</v>
       </c>
@@ -22730,7 +22743,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="462" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A462" s="11" t="s">
         <v>128</v>
       </c>
@@ -22775,7 +22788,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="463" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A463" s="20" t="s">
         <v>128</v>
       </c>
@@ -22820,7 +22833,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="464" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A464" s="23" t="s">
         <v>128</v>
       </c>
@@ -22865,7 +22878,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="465" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A465" s="11" t="s">
         <v>128</v>
       </c>
@@ -22910,7 +22923,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="466" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A466" s="11" t="s">
         <v>128</v>
       </c>
@@ -22955,7 +22968,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="467" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A467" s="11" t="s">
         <v>144</v>
       </c>
@@ -23000,7 +23013,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="468" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A468" s="11" t="s">
         <v>144</v>
       </c>
@@ -23045,7 +23058,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="469" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A469" s="11" t="s">
         <v>144</v>
       </c>
@@ -23090,7 +23103,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="470" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A470" s="23" t="s">
         <v>147</v>
       </c>
@@ -23135,7 +23148,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="471" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A471" s="11" t="s">
         <v>154</v>
       </c>
@@ -23180,7 +23193,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="472" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A472" s="11" t="s">
         <v>154</v>
       </c>
@@ -23225,7 +23238,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="473" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A473" s="20" t="s">
         <v>155</v>
       </c>
@@ -23270,7 +23283,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="474" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A474" s="23" t="s">
         <v>156</v>
       </c>
@@ -23315,7 +23328,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="475" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A475" s="23" t="s">
         <v>156</v>
       </c>
@@ -23358,7 +23371,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="476" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A476" s="20" t="s">
         <v>116</v>
       </c>
@@ -23403,7 +23416,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="477" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A477" s="11" t="s">
         <v>119</v>
       </c>
@@ -23448,7 +23461,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="478" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A478" s="20" t="s">
         <v>160</v>
       </c>
@@ -23493,7 +23506,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="479" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A479" s="23" t="s">
         <v>160</v>
       </c>
@@ -23538,7 +23551,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="480" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A480" s="32" t="s">
         <v>169</v>
       </c>
@@ -23581,7 +23594,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="481" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A481" s="11" t="s">
         <v>169</v>
       </c>
@@ -23626,7 +23639,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="482" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A482" s="23" t="s">
         <v>169</v>
       </c>
@@ -23671,7 +23684,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="483" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:13" s="81" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A483" s="76" t="s">
         <v>179</v>
       </c>
@@ -23716,7 +23729,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="484" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:13" s="81" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A484" s="82" t="s">
         <v>179</v>
       </c>
@@ -23761,7 +23774,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="485" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A485" s="32" t="s">
         <v>186</v>
       </c>
@@ -23804,7 +23817,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="486" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A486" s="11" t="s">
         <v>192</v>
       </c>
@@ -23849,7 +23862,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="487" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A487" s="20" t="s">
         <v>192</v>
       </c>
@@ -23894,7 +23907,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="488" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A488" s="36" t="s">
         <v>199</v>
       </c>
@@ -23939,7 +23952,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="489" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A489" s="36" t="s">
         <v>199</v>
       </c>
@@ -23984,7 +23997,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="490" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A490" s="32" t="s">
         <v>199</v>
       </c>
@@ -24029,7 +24042,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="491" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A491" s="20" t="s">
         <v>202</v>
       </c>
@@ -24072,7 +24085,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="492" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A492" s="20" t="s">
         <v>202</v>
       </c>
@@ -24117,7 +24130,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="493" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A493" s="11" t="s">
         <v>202</v>
       </c>
@@ -24162,7 +24175,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="494" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A494" s="11" t="s">
         <v>202</v>
       </c>
@@ -24207,7 +24220,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="495" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A495" s="61" t="s">
         <v>205</v>
       </c>
@@ -24250,7 +24263,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="496" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A496" s="38" t="s">
         <v>205</v>
       </c>
@@ -24295,7 +24308,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="497" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A497" s="38" t="s">
         <v>205</v>
       </c>
@@ -24338,7 +24351,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="498" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A498" s="38" t="s">
         <v>205</v>
       </c>
@@ -24383,7 +24396,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="499" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A499" s="20" t="s">
         <v>213</v>
       </c>
@@ -24428,7 +24441,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="500" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A500" s="23" t="s">
         <v>213</v>
       </c>
@@ -24473,7 +24486,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="501" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A501" s="32" t="s">
         <v>213</v>
       </c>
@@ -24518,7 +24531,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="502" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A502" s="11" t="s">
         <v>213</v>
       </c>
@@ -24563,7 +24576,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="503" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A503" s="11" t="s">
         <v>222</v>
       </c>
@@ -24609,7 +24622,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="504" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A504" s="11" t="s">
         <v>222</v>
       </c>
@@ -24654,7 +24667,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="505" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A505" s="32" t="s">
         <v>222</v>
       </c>
@@ -24699,7 +24712,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="506" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A506" s="11" t="s">
         <v>225</v>
       </c>
@@ -24744,7 +24757,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="507" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A507" s="23" t="s">
         <v>225</v>
       </c>
@@ -24789,7 +24802,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="508" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A508" s="32" t="s">
         <v>225</v>
       </c>
@@ -24834,7 +24847,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="509" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A509" s="11" t="s">
         <v>225</v>
       </c>
@@ -24879,7 +24892,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="510" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A510" s="20" t="s">
         <v>228</v>
       </c>
@@ -24924,7 +24937,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="511" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A511" s="23" t="s">
         <v>228</v>
       </c>
@@ -24969,7 +24982,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="512" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A512" s="32" t="s">
         <v>228</v>
       </c>
@@ -25012,7 +25025,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="513" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A513" s="11" t="s">
         <v>229</v>
       </c>
@@ -25057,7 +25070,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="514" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A514" s="32" t="s">
         <v>229</v>
       </c>
@@ -25100,7 +25113,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="515" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A515" s="11" t="s">
         <v>230</v>
       </c>
@@ -25145,7 +25158,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="516" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A516" s="32" t="s">
         <v>231</v>
       </c>
@@ -25190,7 +25203,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="517" spans="1:23" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:23" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A517" s="20" t="s">
         <v>231</v>
       </c>
@@ -25245,7 +25258,7 @@
       <c r="V517" s="3"/>
       <c r="W517" s="3"/>
     </row>
-    <row r="518" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A518" s="23" t="s">
         <v>231</v>
       </c>
@@ -25290,7 +25303,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="519" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A519" s="20" t="s">
         <v>231</v>
       </c>
@@ -25335,7 +25348,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="520" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A520" s="23" t="s">
         <v>231</v>
       </c>
@@ -25380,7 +25393,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="521" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A521" s="11" t="s">
         <v>232</v>
       </c>
@@ -25425,7 +25438,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="522" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A522" s="11" t="s">
         <v>232</v>
       </c>
@@ -25468,7 +25481,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="523" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A523" s="20" t="s">
         <v>232</v>
       </c>
@@ -25513,7 +25526,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="524" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A524" s="11" t="s">
         <v>232</v>
       </c>
@@ -25558,7 +25571,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="525" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A525" s="20" t="s">
         <v>232</v>
       </c>
@@ -25603,7 +25616,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="526" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A526" s="23" t="s">
         <v>232</v>
       </c>
@@ -25648,7 +25661,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="527" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A527" s="11" t="s">
         <v>232</v>
       </c>
@@ -25693,7 +25706,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="528" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:23" hidden="1" x14ac:dyDescent="0.35">
       <c r="A528" s="23" t="s">
         <v>232</v>
       </c>
@@ -25736,7 +25749,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="529" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A529" s="11" t="s">
         <v>240</v>
       </c>
@@ -25781,7 +25794,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="530" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A530" s="32" t="s">
         <v>243</v>
       </c>
@@ -25826,7 +25839,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="531" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A531" s="20" t="s">
         <v>244</v>
       </c>
@@ -25871,7 +25884,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="532" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A532" s="20" t="s">
         <v>244</v>
       </c>
@@ -25916,7 +25929,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="533" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A533" s="23" t="s">
         <v>244</v>
       </c>
@@ -25961,7 +25974,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="534" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A534" s="11" t="s">
         <v>244</v>
       </c>
@@ -26006,7 +26019,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="535" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A535" s="23" t="s">
         <v>245</v>
       </c>
@@ -26051,7 +26064,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="536" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A536" s="23" t="s">
         <v>245</v>
       </c>
@@ -26096,7 +26109,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="537" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A537" s="11" t="s">
         <v>245</v>
       </c>
@@ -26131,7 +26144,7 @@
         <v>0</v>
       </c>
       <c r="K537" s="19" t="str">
-        <f t="shared" ref="K537:K568" si="58">IF(E537=0,"Sin Plan",IF(J537&gt;=1,"Completado",IF(J537&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
+        <f t="shared" ref="K537:K539" si="58">IF(E537=0,"Sin Plan",IF(J537&gt;=1,"Completado",IF(J537&gt;0.001,"En Progreso","Pendiente de ejecutar")))</f>
         <v>Sin Plan</v>
       </c>
       <c r="L537" s="6" t="s">
@@ -26141,7 +26154,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="538" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A538" s="32" t="s">
         <v>245</v>
       </c>
@@ -26186,7 +26199,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="539" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A539" s="61" t="s">
         <v>246</v>
       </c>
@@ -26231,7 +26244,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="540" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A540" s="61" t="s">
         <v>246</v>
       </c>
@@ -26262,7 +26275,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="541" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A541" s="61" t="s">
         <v>246</v>
       </c>
@@ -26293,7 +26306,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="542" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A542" s="61" t="s">
         <v>246</v>
       </c>
@@ -26338,7 +26351,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="543" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A543" s="61" t="s">
         <v>246</v>
       </c>
@@ -26371,7 +26384,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="544" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A544" s="61" t="s">
         <v>246</v>
       </c>
@@ -26414,7 +26427,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="545" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A545" s="36" t="s">
         <v>253</v>
       </c>
@@ -26459,7 +26472,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="546" spans="1:13" s="2" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:13" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A546" s="36" t="s">
         <v>253</v>
       </c>
@@ -26504,7 +26517,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="547" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A547" s="36" t="s">
         <v>253</v>
       </c>
@@ -26549,7 +26562,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="548" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A548" s="36" t="s">
         <v>253</v>
       </c>
@@ -26590,7 +26603,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="549" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A549" s="32" t="s">
         <v>258</v>
       </c>
@@ -26635,7 +26648,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="550" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A550" s="20" t="s">
         <v>258</v>
       </c>
@@ -26680,7 +26693,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="551" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A551" s="23" t="s">
         <v>258</v>
       </c>
@@ -26725,7 +26738,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="552" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A552" s="11" t="s">
         <v>258</v>
       </c>
@@ -26770,7 +26783,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="553" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A553" s="23" t="s">
         <v>258</v>
       </c>
@@ -26815,7 +26828,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="554" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A554" s="23" t="s">
         <v>261</v>
       </c>
@@ -26860,7 +26873,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="555" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A555" s="20" t="s">
         <v>261</v>
       </c>
@@ -26905,7 +26918,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="556" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A556" s="11" t="s">
         <v>261</v>
       </c>
@@ -26950,7 +26963,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="557" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A557" s="11" t="s">
         <v>261</v>
       </c>
@@ -26991,7 +27004,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="558" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A558" s="20" t="s">
         <v>262</v>
       </c>
@@ -27036,7 +27049,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="559" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A559" s="20" t="s">
         <v>262</v>
       </c>
@@ -27081,7 +27094,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="560" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A560" s="23" t="s">
         <v>265</v>
       </c>
@@ -27126,7 +27139,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="561" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A561" s="23" t="s">
         <v>265</v>
       </c>
@@ -27172,7 +27185,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="562" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A562" s="11" t="s">
         <v>267</v>
       </c>
@@ -27217,7 +27230,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="563" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A563" s="23" t="s">
         <v>270</v>
       </c>
@@ -27262,7 +27275,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="564" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A564" s="20" t="s">
         <v>270</v>
       </c>
@@ -27307,7 +27320,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="565" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A565" s="23" t="s">
         <v>270</v>
       </c>
@@ -27352,7 +27365,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="566" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A566" s="11" t="s">
         <v>270</v>
       </c>
@@ -27395,7 +27408,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="567" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A567" s="11" t="s">
         <v>270</v>
       </c>
@@ -27440,7 +27453,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="568" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A568" s="11" t="s">
         <v>270</v>
       </c>
@@ -27485,7 +27498,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="569" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A569" s="20" t="s">
         <v>270</v>
       </c>
@@ -27530,7 +27543,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="570" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A570" s="11" t="s">
         <v>270</v>
       </c>
@@ -27575,7 +27588,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="571" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A571" s="11" t="s">
         <v>270</v>
       </c>
@@ -27620,7 +27633,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="572" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A572" s="11" t="s">
         <v>270</v>
       </c>
@@ -27665,7 +27678,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="573" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A573" s="11" t="s">
         <v>270</v>
       </c>
@@ -27710,7 +27723,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="574" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A574" s="23" t="s">
         <v>272</v>
       </c>
@@ -27755,7 +27768,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="575" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A575" s="11" t="s">
         <v>272</v>
       </c>
@@ -27800,7 +27813,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="576" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A576" s="23" t="s">
         <v>277</v>
       </c>
@@ -27845,7 +27858,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="577" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A577" s="11" t="s">
         <v>281</v>
       </c>
@@ -27890,7 +27903,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="578" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A578" s="23" t="s">
         <v>283</v>
       </c>
@@ -27935,7 +27948,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="579" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A579" s="11" t="s">
         <v>286</v>
       </c>
@@ -27980,7 +27993,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="580" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A580" s="23" t="s">
         <v>287</v>
       </c>
@@ -28025,7 +28038,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="581" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A581" s="11" t="s">
         <v>288</v>
       </c>
@@ -28070,7 +28083,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="582" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A582" s="11" t="s">
         <v>289</v>
       </c>
@@ -28115,7 +28128,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="583" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A583" s="32" t="s">
         <v>289</v>
       </c>
@@ -28160,7 +28173,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="584" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A584" s="32" t="s">
         <v>292</v>
       </c>
@@ -28206,7 +28219,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="585" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A585" s="11" t="s">
         <v>294</v>
       </c>
@@ -28251,7 +28264,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="586" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A586" s="32" t="s">
         <v>294</v>
       </c>
@@ -28294,7 +28307,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="587" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A587" s="20" t="s">
         <v>294</v>
       </c>
@@ -28339,7 +28352,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="588" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A588" s="11" t="s">
         <v>297</v>
       </c>
@@ -28382,7 +28395,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="589" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A589" s="23" t="s">
         <v>297</v>
       </c>
@@ -28427,7 +28440,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="590" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A590" s="32" t="s">
         <v>297</v>
       </c>
@@ -28470,7 +28483,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="591" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A591" s="11" t="s">
         <v>297</v>
       </c>
@@ -28513,7 +28526,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="592" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A592" s="11" t="s">
         <v>297</v>
       </c>
@@ -28558,7 +28571,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="593" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A593" s="11" t="s">
         <v>299</v>
       </c>
@@ -28603,7 +28616,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="594" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A594" s="23" t="s">
         <v>300</v>
       </c>
@@ -28648,7 +28661,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="595" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A595" s="11" t="s">
         <v>300</v>
       </c>
@@ -28693,7 +28706,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="596" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A596" s="11" t="s">
         <v>300</v>
       </c>
@@ -28738,7 +28751,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="597" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A597" s="23" t="s">
         <v>300</v>
       </c>
@@ -28783,7 +28796,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="598" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A598" s="11" t="s">
         <v>300</v>
       </c>
@@ -28828,7 +28841,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="599" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A599" s="11" t="s">
         <v>300</v>
       </c>
@@ -28873,7 +28886,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="600" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A600" s="20" t="s">
         <v>302</v>
       </c>
@@ -28918,7 +28931,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="601" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A601" s="23" t="s">
         <v>306</v>
       </c>
@@ -28964,7 +28977,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="602" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A602" s="20" t="s">
         <v>306</v>
       </c>
@@ -29009,7 +29022,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="603" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A603" s="23" t="s">
         <v>120</v>
       </c>
@@ -29054,7 +29067,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="604" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A604" s="70" t="s">
         <v>118</v>
       </c>
@@ -29091,7 +29104,7 @@
       </c>
       <c r="M604" s="6"/>
     </row>
-    <row r="605" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A605" s="11" t="s">
         <v>119</v>
       </c>
@@ -29136,7 +29149,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="606" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A606" s="20" t="s">
         <v>119</v>
       </c>
@@ -29181,7 +29194,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="607" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A607" s="11" t="s">
         <v>119</v>
       </c>
@@ -29226,7 +29239,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="608" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A608" s="20" t="s">
         <v>119</v>
       </c>
@@ -29271,7 +29284,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="609" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A609" s="11" t="s">
         <v>120</v>
       </c>
@@ -29316,7 +29329,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="610" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A610" s="20" t="s">
         <v>120</v>
       </c>
@@ -29361,7 +29374,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="611" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A611" s="70" t="s">
         <v>120</v>
       </c>
@@ -29398,7 +29411,7 @@
       </c>
       <c r="M611" s="6"/>
     </row>
-    <row r="612" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A612" s="23" t="s">
         <v>121</v>
       </c>
@@ -29443,7 +29456,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="613" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A613" s="20" t="s">
         <v>156</v>
       </c>
@@ -29473,7 +29486,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="614" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A614" s="32" t="s">
         <v>199</v>
       </c>
@@ -29503,7 +29516,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="615" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A615" s="20" t="s">
         <v>202</v>
       </c>
@@ -29538,7 +29551,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="616" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A616" s="38" t="s">
         <v>205</v>
       </c>
@@ -29571,7 +29584,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="617" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A617" s="11" t="s">
         <v>210</v>
       </c>
@@ -29604,7 +29617,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="618" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A618" s="23" t="s">
         <v>225</v>
       </c>
@@ -29639,7 +29652,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="619" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A619" s="11" t="s">
         <v>232</v>
       </c>
@@ -29673,7 +29686,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="620" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A620" s="11" t="s">
         <v>232</v>
       </c>
@@ -29706,7 +29719,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="621" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A621" s="32" t="s">
         <v>232</v>
       </c>
@@ -29739,7 +29752,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="622" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A622" s="32" t="s">
         <v>232</v>
       </c>
@@ -29772,7 +29785,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="623" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A623" s="32" t="s">
         <v>232</v>
       </c>
@@ -29806,7 +29819,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="624" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A624" s="11" t="s">
         <v>232</v>
       </c>
@@ -29840,7 +29853,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="625" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A625" s="11" t="s">
         <v>243</v>
       </c>
@@ -29873,7 +29886,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="626" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A626" s="61" t="s">
         <v>246</v>
       </c>
@@ -29916,7 +29929,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="627" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A627" s="61" t="s">
         <v>246</v>
       </c>
@@ -29959,7 +29972,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="628" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A628" s="61" t="s">
         <v>246</v>
       </c>
@@ -29988,7 +30001,7 @@
       </c>
       <c r="M628" s="6"/>
     </row>
-    <row r="629" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A629" s="61" t="s">
         <v>246</v>
       </c>
@@ -30029,7 +30042,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="630" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A630" s="61" t="s">
         <v>246</v>
       </c>
@@ -30070,7 +30083,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="631" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A631" s="36" t="s">
         <v>253</v>
       </c>
@@ -30104,7 +30117,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="632" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A632" s="36" t="s">
         <v>253</v>
       </c>
@@ -30134,7 +30147,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="633" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A633" s="11" t="s">
         <v>267</v>
       </c>
@@ -30177,7 +30190,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="634" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A634" s="32" t="s">
         <v>292</v>
       </c>
@@ -30207,7 +30220,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="635" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A635" s="23" t="s">
         <v>294</v>
       </c>
@@ -30238,7 +30251,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="636" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A636" s="23" t="s">
         <v>297</v>
       </c>
@@ -30267,7 +30280,7 @@
       </c>
       <c r="M636" s="6"/>
     </row>
-    <row r="637" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A637" s="53" t="s">
         <v>297</v>
       </c>
@@ -30295,7 +30308,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="638" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A638" s="20" t="s">
         <v>303</v>
       </c>
@@ -30325,7 +30338,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="639" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A639" s="52" t="s">
         <v>306</v>
       </c>
@@ -30355,7 +30368,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="640" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A640" s="49" t="s">
         <v>232</v>
       </c>
@@ -30383,7 +30396,7 @@
       </c>
       <c r="M640" s="6"/>
     </row>
-    <row r="641" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A641" s="49" t="s">
         <v>265</v>
       </c>
@@ -30411,7 +30424,7 @@
       </c>
       <c r="M641" s="6"/>
     </row>
-    <row r="642" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A642" s="65" t="s">
         <v>205</v>
       </c>
@@ -30439,7 +30452,7 @@
       </c>
       <c r="M642" s="6"/>
     </row>
-    <row r="643" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A643" s="65" t="s">
         <v>205</v>
       </c>
@@ -30467,7 +30480,7 @@
       </c>
       <c r="M643" s="6"/>
     </row>
-    <row r="644" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A644" s="65" t="s">
         <v>169</v>
       </c>
@@ -30495,7 +30508,7 @@
       </c>
       <c r="M644" s="6"/>
     </row>
-    <row r="645" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A645" s="65" t="s">
         <v>186</v>
       </c>
@@ -30523,7 +30536,7 @@
       </c>
       <c r="M645" s="6"/>
     </row>
-    <row r="646" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A646" s="52" t="s">
         <v>122</v>
       </c>
@@ -30568,7 +30581,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="647" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A647" s="72" t="s">
         <v>122</v>
       </c>
@@ -30604,7 +30617,7 @@
       </c>
       <c r="M647" s="6"/>
     </row>
-    <row r="648" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A648" s="49" t="s">
         <v>123</v>
       </c>
@@ -30649,7 +30662,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="649" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A649" s="49" t="s">
         <v>123</v>
       </c>
@@ -30694,7 +30707,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="650" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A650" s="49" t="s">
         <v>124</v>
       </c>
@@ -30739,7 +30752,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="651" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A651" s="72" t="s">
         <v>124</v>
       </c>
@@ -30775,7 +30788,7 @@
       </c>
       <c r="M651" s="6"/>
     </row>
-    <row r="652" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A652" s="49" t="s">
         <v>157</v>
       </c>
@@ -30820,7 +30833,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="653" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A653" s="73" t="s">
         <v>157</v>
       </c>
@@ -30865,7 +30878,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="654" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A654" s="52" t="s">
         <v>157</v>
       </c>
@@ -30910,7 +30923,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="655" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A655" s="73" t="s">
         <v>157</v>
       </c>
@@ -30955,7 +30968,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="656" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A656" s="52" t="s">
         <v>157</v>
       </c>
@@ -31000,7 +31013,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="657" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A657" s="52" t="s">
         <v>57</v>
       </c>
@@ -31045,7 +31058,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="658" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A658" s="73" t="s">
         <v>82</v>
       </c>
@@ -31084,7 +31097,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="659" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A659" s="73" t="s">
         <v>157</v>
       </c>
@@ -31129,7 +31142,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="660" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A660" s="72" t="s">
         <v>128</v>
       </c>
@@ -31157,7 +31170,7 @@
       </c>
       <c r="M660" s="6"/>
     </row>
-    <row r="661" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A661" s="72" t="s">
         <v>155</v>
       </c>
@@ -31185,7 +31198,7 @@
       </c>
       <c r="M661" s="6"/>
     </row>
-    <row r="662" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A662" s="72" t="s">
         <v>156</v>
       </c>
@@ -31213,7 +31226,7 @@
       </c>
       <c r="M662" s="6"/>
     </row>
-    <row r="663" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A663" s="72" t="s">
         <v>272</v>
       </c>
@@ -31241,7 +31254,7 @@
       </c>
       <c r="M663" s="6"/>
     </row>
-    <row r="664" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A664" s="72" t="s">
         <v>282</v>
       </c>
@@ -31269,7 +31282,7 @@
       </c>
       <c r="M664" s="6"/>
     </row>
-    <row r="665" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:13" s="81" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A665" s="88" t="s">
         <v>179</v>
       </c>
@@ -31314,7 +31327,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="666" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:13" s="81" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A666" s="86" t="s">
         <v>179</v>
       </c>
@@ -31359,7 +31372,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="667" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:13" s="81" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A667" s="90" t="s">
         <v>179</v>
       </c>
@@ -31404,7 +31417,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="668" spans="1:13" s="81" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:13" s="81" customFormat="1" hidden="1" x14ac:dyDescent="0.35">
       <c r="A668" s="86" t="s">
         <v>179</v>
       </c>
@@ -31449,7 +31462,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="669" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A669" s="65" t="s">
         <v>179</v>
       </c>
@@ -31494,7 +31507,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="670" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A670" s="65" t="s">
         <v>179</v>
       </c>
@@ -31525,7 +31538,7 @@
       </c>
       <c r="M670" s="6"/>
     </row>
-    <row r="671" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A671" s="65" t="s">
         <v>202</v>
       </c>
@@ -31556,7 +31569,7 @@
       </c>
       <c r="M671" s="6"/>
     </row>
-    <row r="672" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A672" s="65" t="s">
         <v>199</v>
       </c>
@@ -31587,7 +31600,7 @@
       </c>
       <c r="M672" s="6"/>
     </row>
-    <row r="673" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A673" s="65" t="s">
         <v>225</v>
       </c>
@@ -31616,7 +31629,7 @@
       </c>
       <c r="M673" s="6"/>
     </row>
-    <row r="674" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A674" s="65" t="s">
         <v>225</v>
       </c>
@@ -31645,7 +31658,7 @@
       </c>
       <c r="M674" s="6"/>
     </row>
-    <row r="675" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A675" s="65" t="s">
         <v>243</v>
       </c>
@@ -31674,7 +31687,7 @@
       </c>
       <c r="M675" s="6"/>
     </row>
-    <row r="676" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A676" s="65" t="s">
         <v>267</v>
       </c>
@@ -31703,7 +31716,7 @@
       </c>
       <c r="M676" s="6"/>
     </row>
-    <row r="677" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A677" s="65" t="s">
         <v>222</v>
       </c>
@@ -31732,7 +31745,7 @@
       </c>
       <c r="M677" s="6"/>
     </row>
-    <row r="678" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A678" s="65" t="s">
         <v>232</v>
       </c>
@@ -31761,7 +31774,7 @@
       </c>
       <c r="M678" s="6"/>
     </row>
-    <row r="679" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A679" s="65" t="s">
         <v>244</v>
       </c>
@@ -31790,7 +31803,7 @@
       </c>
       <c r="M679" s="6"/>
     </row>
-    <row r="680" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A680" s="65" t="s">
         <v>294</v>
       </c>
@@ -31819,7 +31832,7 @@
       </c>
       <c r="M680" s="6"/>
     </row>
-    <row r="681" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A681" s="65" t="s">
         <v>297</v>
       </c>
@@ -31848,7 +31861,7 @@
       </c>
       <c r="M681" s="6"/>
     </row>
-    <row r="682" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A682" s="65" t="s">
         <v>299</v>
       </c>
@@ -31877,7 +31890,7 @@
       </c>
       <c r="M682" s="6"/>
     </row>
-    <row r="683" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A683" s="65" t="s">
         <v>303</v>
       </c>
@@ -31906,7 +31919,7 @@
       </c>
       <c r="M683" s="6"/>
     </row>
-    <row r="684" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A684" s="65" t="s">
         <v>306</v>
       </c>
@@ -31935,7 +31948,7 @@
       </c>
       <c r="M684" s="6"/>
     </row>
-    <row r="685" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:13" hidden="1" x14ac:dyDescent="0.35">
       <c r="A685" s="65" t="s">
         <v>147</v>
       </c>
